--- a/business-libraries/test-data/student_case/assessment.xlsx
+++ b/business-libraries/test-data/student_case/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:Q3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,102 +419,51 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
-        <v>适用年级</v>
+        <v>施测对象*</v>
       </c>
       <c r="G1" t="str">
-        <v>适用学科</v>
+        <v>施测形式*</v>
       </c>
       <c r="H1" t="str">
-        <v>施测对象*</v>
+        <v>触发方式*</v>
       </c>
       <c r="I1" t="str">
-        <v>施测形式*</v>
+        <v>作答频次*</v>
       </c>
       <c r="J1" t="str">
-        <v>触发方式*</v>
+        <v>是否必做*</v>
       </c>
       <c r="K1" t="str">
-        <v>作答频次*</v>
+        <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
-        <v>是否必做*</v>
+        <v>结果可见性*</v>
       </c>
       <c r="M1" t="str">
-        <v>预计用时分钟*</v>
+        <v>数据敏感级*</v>
       </c>
       <c r="N1" t="str">
-        <v>作答时限分钟</v>
+        <v>来源属性*</v>
       </c>
       <c r="O1" t="str">
-        <v>最低题数</v>
+        <v>手册出处*</v>
       </c>
       <c r="P1" t="str">
-        <v>使用时机</v>
+        <v>版本*</v>
       </c>
       <c r="Q1" t="str">
-        <v>重评间隔天数</v>
-      </c>
-      <c r="R1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="S1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="T1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>责任角色</v>
-      </c>
-      <c r="V1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="W1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="X1" t="str">
-        <v>外部授权说明</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="AA1" t="str">
         <v>量表说明</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>常模参照</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>信度说明</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>效度说明</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>隐私声明</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>适用前提</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>不适合情况</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>后续建议动作</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B2" t="str">
-        <v>学生个体问题学生行为问题五问</v>
+        <v>学生个体问题快速筛查</v>
       </c>
       <c r="C2" t="str">
-        <v>行为问题</v>
+        <v>五类筛查</v>
       </c>
       <c r="D2" t="str">
         <v>student_case</v>
@@ -523,102 +472,51 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H2" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I2" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J2" t="str">
-        <v>manual</v>
+        <v>是</v>
       </c>
       <c r="K2" t="str">
-        <v>monthly</v>
+        <v>6</v>
       </c>
       <c r="L2" t="str">
-        <v>是</v>
+        <v>teacher_only</v>
       </c>
       <c r="M2" t="str">
-        <v>3</v>
+        <v>sensitive</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="O2" t="str">
-        <v>5</v>
+        <v>学生个体问题手册v1</v>
       </c>
       <c r="P2" t="str">
-        <v>每月一次</v>
+        <v>1.0.0</v>
       </c>
       <c r="Q2" t="str">
-        <v>30</v>
-      </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="U2" t="str">
-        <v>班主任本人</v>
-      </c>
-      <c r="V2" t="str">
-        <v>highly_sensitive</v>
-      </c>
-      <c r="W2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v>技术理论手册V5 第3章</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>回顾最近一周状态，产出多维评估结果</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>全国中小学班主任常模 N=3200</v>
-      </c>
-      <c r="AC2" t="str">
-        <v>Cronbach α=0.87</v>
-      </c>
-      <c r="AD2" t="str">
-        <v>与GHQ-12 相关系数 r=0.64</v>
-      </c>
-      <c r="AE2" t="str">
-        <v>数据仅用于教学支持，不用于人事考核</v>
-      </c>
-      <c r="AF2" t="str">
-        <v>适用于在职班主任，不适用于实习或代课教师</v>
-      </c>
-      <c r="AG2" t="str">
-        <v>教师正在经历重大个人变故时，建议先转介心理支持再施测</v>
-      </c>
-      <c r="AH2" t="str">
-        <v>如总分&gt;=17，建议进行深度访谈并启动个案</v>
+        <v>从学业、行为、情绪、社交和适应五类表现进行教育场景筛查，不构成医学诊断。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ST_QUICK</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B3" t="str">
-        <v>学生个体问题学业动机评估</v>
+        <v>EBRCA 结构化观察记录</v>
       </c>
       <c r="C3" t="str">
-        <v>学业动机</v>
+        <v>EBRCA</v>
       </c>
       <c r="D3" t="str">
         <v>student_case</v>
@@ -627,103 +525,52 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H3" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I3" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J3" t="str">
-        <v>manual</v>
+        <v>否</v>
       </c>
       <c r="K3" t="str">
-        <v>per_case</v>
+        <v>8</v>
       </c>
       <c r="L3" t="str">
-        <v>是</v>
+        <v>teacher_only</v>
       </c>
       <c r="M3" t="str">
-        <v>5</v>
+        <v>sensitive</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="O3" t="str">
-        <v>8</v>
+        <v>学生个体问题手册v1</v>
       </c>
       <c r="P3" t="str">
-        <v>学期初/学期末</v>
+        <v>1.0.0</v>
       </c>
       <c r="Q3" t="str">
-        <v>90</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="U3" t="str">
-        <v>班主任本人</v>
-      </c>
-      <c r="V3" t="str">
-        <v>internal</v>
-      </c>
-      <c r="W3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <v>技术理论手册V5 第4章</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>评估教师在学生个体问题相关维度的资源与压力状况</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>全国中小学班主任常模 N=2800</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>Cronbach α=0.82</v>
-      </c>
-      <c r="AD3" t="str">
-        <v>内容效度经专家评审</v>
-      </c>
-      <c r="AE3" t="str">
-        <v>数据仅用于教学支持</v>
-      </c>
-      <c r="AF3" t="str">
-        <v>适用于在职班主任</v>
-      </c>
-      <c r="AG3" t="str">
-        <v>教师在严重心理危机时，建议先进行心理评估</v>
-      </c>
-      <c r="AH3" t="str">
-        <v>根据评估结果推荐相应的支持工具</v>
+        <v>在五类筛查提示需要深入了解后使用，按事件—行为—结果—诱因—已尝试支持做结构化观察。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:J22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -739,552 +586,706 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
-        <v>子维度</v>
+        <v>题干*</v>
       </c>
       <c r="F1" t="str">
-        <v>题干*</v>
+        <v>选项组编码*</v>
       </c>
       <c r="G1" t="str">
-        <v>题干举例</v>
+        <v>反向计分*</v>
       </c>
       <c r="H1" t="str">
-        <v>选项组编码*</v>
+        <v>权重</v>
       </c>
       <c r="I1" t="str">
-        <v>反向计分*</v>
+        <v>是否必答*</v>
       </c>
       <c r="J1" t="str">
-        <v>权重</v>
-      </c>
-      <c r="K1" t="str">
-        <v>是否必答*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>显示条件</v>
-      </c>
-      <c r="M1" t="str">
         <v>数据用途*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>答题提示</v>
-      </c>
-      <c r="O1" t="str">
-        <v>题目说明</v>
-      </c>
-      <c r="P1" t="str">
-        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B2" t="str">
-        <v>q1</v>
+        <v>aca1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>EMOTION</v>
+        <v>学业表现</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>学习表现近期出现持续且明显的下降。</v>
       </c>
       <c r="F2" t="str">
-        <v>这一周，我有多少时间感到学生情绪困扰程度？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H2" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>1</v>
-      </c>
-      <c r="K2" t="str">
-        <v>是</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B3" t="str">
-        <v>q2</v>
+        <v>aca2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
       </c>
       <c r="D3" t="str">
-        <v>BEHAVIOR</v>
+        <v>学业表现</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>完成作业、听课或考试受到明显影响。</v>
       </c>
       <c r="F3" t="str">
-        <v>这一周，我有多少时间感到学生问题行为频率和严重度？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H3" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J3" t="str">
-        <v>1</v>
-      </c>
-      <c r="K3" t="str">
-        <v>是</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B4" t="str">
-        <v>q3</v>
+        <v>aca3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
       </c>
       <c r="D4" t="str">
-        <v>MOTIVATION</v>
+        <v>学业表现</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>已有常规支持措施没有带来改善。</v>
       </c>
       <c r="F4" t="str">
-        <v>这一周，我有多少时间感到学生学习的内外在动机？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H4" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
-        <v>1</v>
-      </c>
-      <c r="K4" t="str">
-        <v>是</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B5" t="str">
-        <v>q4</v>
+        <v>beh1</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>RELATION</v>
+        <v>行为表现</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>冲动、对抗或规则破坏行为频繁出现。</v>
       </c>
       <c r="F5" t="str">
-        <v>这一周，我有多少时间感到学生与同伴和教师的关系质量？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H5" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J5" t="str">
-        <v>1</v>
-      </c>
-      <c r="K5" t="str">
-        <v>是</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B6" t="str">
-        <v>q5</v>
+        <v>beh2</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>SELF_ESTEEM</v>
+        <v>行为表现</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>行为已经明显影响本人或同伴的学习。</v>
       </c>
       <c r="F6" t="str">
-        <v>这一周，我有多少时间感到学生的自我价值感？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H6" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J6" t="str">
-        <v>1</v>
-      </c>
-      <c r="K6" t="str">
-        <v>是</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ST_QUICK</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B7" t="str">
-        <v>q1</v>
+        <v>beh3</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>EMOTION</v>
+        <v>行为表现</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>行为发生的场景和诱因较难预测。</v>
       </c>
       <c r="F7" t="str">
-        <v>在学生个体问题方面，评估学生情绪困扰程度的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H7" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J7" t="str">
-        <v>1</v>
-      </c>
-      <c r="K7" t="str">
-        <v>是</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ST_QUICK</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B8" t="str">
-        <v>q2</v>
+        <v>emo1</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>BEHAVIOR</v>
+        <v>情绪状态</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>持续出现低落、焦虑、易怒或明显退缩。</v>
       </c>
       <c r="F8" t="str">
-        <v>在学生个体问题方面，评估学生问题行为频率和严重度的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H8" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J8" t="str">
-        <v>1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>是</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ST_QUICK</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B9" t="str">
-        <v>q3</v>
+        <v>emo2</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>MOTIVATION</v>
+        <v>情绪状态</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>情绪变化已经影响日常功能。</v>
       </c>
       <c r="F9" t="str">
-        <v>在学生个体问题方面，评估学生学习的内外在动机的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H9" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
-        <v>1</v>
-      </c>
-      <c r="K9" t="str">
-        <v>是</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ST_QUICK</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B10" t="str">
-        <v>q4</v>
+        <v>emo3</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>RELATION</v>
+        <v>情绪状态</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>学生很难表达或调节当前感受。</v>
       </c>
       <c r="F10" t="str">
-        <v>在学生个体问题方面，评估学生与同伴和教师的关系质量的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H10" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J10" t="str">
-        <v>1</v>
-      </c>
-      <c r="K10" t="str">
-        <v>是</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v>5</v>
+        <v>compute</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ST_QUICK</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B11" t="str">
-        <v>q5</v>
+        <v>soc1</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>SELF_ESTEEM</v>
+        <v>同伴社交</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>与同伴的冲突、排斥或孤立反复发生。</v>
       </c>
       <c r="F11" t="str">
-        <v>在学生个体问题方面，评估学生的自我价值感的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H11" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J11" t="str">
-        <v>1</v>
-      </c>
-      <c r="K11" t="str">
-        <v>是</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v>5</v>
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="B12" t="str">
+        <v>soc2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>single</v>
+      </c>
+      <c r="D12" t="str">
+        <v>同伴社交</v>
+      </c>
+      <c r="E12" t="str">
+        <v>学生缺少稳定的同伴支持。</v>
+      </c>
+      <c r="F12" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G12" t="str">
+        <v>否</v>
+      </c>
+      <c r="H12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I12" t="str">
+        <v>是</v>
+      </c>
+      <c r="J12" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="B13" t="str">
+        <v>soc3</v>
+      </c>
+      <c r="C13" t="str">
+        <v>single</v>
+      </c>
+      <c r="D13" t="str">
+        <v>同伴社交</v>
+      </c>
+      <c r="E13" t="str">
+        <v>常规关系修复方式效果有限。</v>
+      </c>
+      <c r="F13" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G13" t="str">
+        <v>否</v>
+      </c>
+      <c r="H13" t="str">
+        <v>1</v>
+      </c>
+      <c r="I13" t="str">
+        <v>是</v>
+      </c>
+      <c r="J13" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="B14" t="str">
+        <v>adp1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>single</v>
+      </c>
+      <c r="D14" t="str">
+        <v>适应状况</v>
+      </c>
+      <c r="E14" t="str">
+        <v>在转班、家庭变化或重要事件后持续难以适应。</v>
+      </c>
+      <c r="F14" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G14" t="str">
+        <v>否</v>
+      </c>
+      <c r="H14" t="str">
+        <v>1</v>
+      </c>
+      <c r="I14" t="str">
+        <v>是</v>
+      </c>
+      <c r="J14" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="B15" t="str">
+        <v>adp2</v>
+      </c>
+      <c r="C15" t="str">
+        <v>single</v>
+      </c>
+      <c r="D15" t="str">
+        <v>适应状况</v>
+      </c>
+      <c r="E15" t="str">
+        <v>出现明显躯体不适、拒学或回避。</v>
+      </c>
+      <c r="F15" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G15" t="str">
+        <v>否</v>
+      </c>
+      <c r="H15" t="str">
+        <v>1</v>
+      </c>
+      <c r="I15" t="str">
+        <v>是</v>
+      </c>
+      <c r="J15" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="B16" t="str">
+        <v>adp3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>single</v>
+      </c>
+      <c r="D16" t="str">
+        <v>适应状况</v>
+      </c>
+      <c r="E16" t="str">
+        <v>问题持续四周以上且没有改善趋势。</v>
+      </c>
+      <c r="F16" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G16" t="str">
+        <v>否</v>
+      </c>
+      <c r="H16" t="str">
+        <v>1</v>
+      </c>
+      <c r="I16" t="str">
+        <v>是</v>
+      </c>
+      <c r="J16" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="B17" t="str">
+        <v>ob1</v>
+      </c>
+      <c r="C17" t="str">
+        <v>single</v>
+      </c>
+      <c r="D17" t="str">
+        <v>诱因清晰度</v>
+      </c>
+      <c r="E17" t="str">
+        <v>行为发生前的情境难以识别。</v>
+      </c>
+      <c r="F17" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G17" t="str">
+        <v>否</v>
+      </c>
+      <c r="H17" t="str">
+        <v>1</v>
+      </c>
+      <c r="I17" t="str">
+        <v>是</v>
+      </c>
+      <c r="J17" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ob2</v>
+      </c>
+      <c r="C18" t="str">
+        <v>single</v>
+      </c>
+      <c r="D18" t="str">
+        <v>诱因清晰度</v>
+      </c>
+      <c r="E18" t="str">
+        <v>同样的情境下行为反应不一致。</v>
+      </c>
+      <c r="F18" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G18" t="str">
+        <v>否</v>
+      </c>
+      <c r="H18" t="str">
+        <v>1</v>
+      </c>
+      <c r="I18" t="str">
+        <v>是</v>
+      </c>
+      <c r="J18" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="B19" t="str">
+        <v>ob3</v>
+      </c>
+      <c r="C19" t="str">
+        <v>single</v>
+      </c>
+      <c r="D19" t="str">
+        <v>功能影响</v>
+      </c>
+      <c r="E19" t="str">
+        <v>该表现已影响学生完成日常学习任务。</v>
+      </c>
+      <c r="F19" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G19" t="str">
+        <v>否</v>
+      </c>
+      <c r="H19" t="str">
+        <v>1</v>
+      </c>
+      <c r="I19" t="str">
+        <v>是</v>
+      </c>
+      <c r="J19" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ob4</v>
+      </c>
+      <c r="C20" t="str">
+        <v>single</v>
+      </c>
+      <c r="D20" t="str">
+        <v>功能影响</v>
+      </c>
+      <c r="E20" t="str">
+        <v>该表现已影响学生与他人的正常互动。</v>
+      </c>
+      <c r="F20" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G20" t="str">
+        <v>否</v>
+      </c>
+      <c r="H20" t="str">
+        <v>1</v>
+      </c>
+      <c r="I20" t="str">
+        <v>是</v>
+      </c>
+      <c r="J20" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="B21" t="str">
+        <v>ob5</v>
+      </c>
+      <c r="C21" t="str">
+        <v>single</v>
+      </c>
+      <c r="D21" t="str">
+        <v>既有支持有效性</v>
+      </c>
+      <c r="E21" t="str">
+        <v>已尝试的座位调整、谈话等措施没有带来改善。</v>
+      </c>
+      <c r="F21" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G21" t="str">
+        <v>否</v>
+      </c>
+      <c r="H21" t="str">
+        <v>1</v>
+      </c>
+      <c r="I21" t="str">
+        <v>是</v>
+      </c>
+      <c r="J21" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="B22" t="str">
+        <v>ob6</v>
+      </c>
+      <c r="C22" t="str">
+        <v>single</v>
+      </c>
+      <c r="D22" t="str">
+        <v>既有支持有效性</v>
+      </c>
+      <c r="E22" t="str">
+        <v>家庭配合的支持措施没有带来改善。</v>
+      </c>
+      <c r="F22" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G22" t="str">
+        <v>否</v>
+      </c>
+      <c r="H22" t="str">
+        <v>1</v>
+      </c>
+      <c r="I22" t="str">
+        <v>是</v>
+      </c>
+      <c r="J22" t="str">
+        <v>compute</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1370,16 +1371,86 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>3</v>
+      </c>
+      <c r="C9" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D9" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>4</v>
+      </c>
+      <c r="C10" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B11" t="str">
+        <v>5</v>
+      </c>
+      <c r="C11" t="str">
+        <v>非常符合</v>
+      </c>
+      <c r="D11" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:I9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1409,25 +1480,19 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
-      <c r="J1" t="str">
-        <v>常模均值</v>
-      </c>
-      <c r="K1" t="str">
-        <v>常模标准差</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B2" t="str">
-        <v>EMOTION</v>
+        <v>SC_ACADEMIC</v>
       </c>
       <c r="C2" t="str">
-        <v>情绪问题</v>
+        <v>学业表现</v>
       </c>
       <c r="D2" t="str">
-        <v>q1</v>
+        <v>aca1,aca2,aca3</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1436,33 +1501,27 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>评估学生情绪困扰程度</v>
+        <v>学业表现维度</v>
       </c>
       <c r="H2" t="str">
-        <v>&gt;=4 分：情绪困扰严重</v>
+        <v>学业表现持续下降且常规支持无效</v>
       </c>
       <c r="I2" t="str">
-        <v>&lt;=2 分：情绪稳定</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2.5</v>
-      </c>
-      <c r="K2" t="str">
-        <v>1.0</v>
+        <v>学业表现稳定</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B3" t="str">
-        <v>BEHAVIOR</v>
+        <v>SC_BEHAVIOR</v>
       </c>
       <c r="C3" t="str">
-        <v>行为问题</v>
+        <v>行为表现</v>
       </c>
       <c r="D3" t="str">
-        <v>q2</v>
+        <v>beh1,beh2,beh3</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1471,33 +1530,27 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>评估学生问题行为频率和严重度</v>
+        <v>行为表现维度</v>
       </c>
       <c r="H3" t="str">
-        <v>&gt;=4 分：行为问题突出</v>
+        <v>冲动或对抗行为频繁且难以预测</v>
       </c>
       <c r="I3" t="str">
-        <v>&lt;=2 分：行为规范</v>
-      </c>
-      <c r="J3" t="str">
-        <v>2.3</v>
-      </c>
-      <c r="K3" t="str">
-        <v>1.05</v>
+        <v>行为表现可控</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B4" t="str">
-        <v>MOTIVATION</v>
+        <v>SC_EMOTION</v>
       </c>
       <c r="C4" t="str">
-        <v>学习动机</v>
+        <v>情绪状态</v>
       </c>
       <c r="D4" t="str">
-        <v>q3</v>
+        <v>emo1,emo2,emo3</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1506,33 +1559,27 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>评估学生学习的内外在动机</v>
+        <v>情绪状态维度</v>
       </c>
       <c r="H4" t="str">
-        <v>&gt;=4 分：动机强烈</v>
+        <v>持续低落焦虑且影响日常功能</v>
       </c>
       <c r="I4" t="str">
-        <v>&lt;=2 分：动机缺失</v>
-      </c>
-      <c r="J4" t="str">
-        <v>2.9</v>
-      </c>
-      <c r="K4" t="str">
-        <v>0.9</v>
+        <v>情绪状态平稳</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B5" t="str">
-        <v>RELATION</v>
+        <v>SC_SOCIAL</v>
       </c>
       <c r="C5" t="str">
-        <v>人际关系</v>
+        <v>同伴社交</v>
       </c>
       <c r="D5" t="str">
-        <v>q4</v>
+        <v>soc1,soc2,soc3</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1541,33 +1588,27 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>评估学生与同伴和教师的关系质量</v>
+        <v>同伴社交维度</v>
       </c>
       <c r="H5" t="str">
-        <v>&gt;=4 分：关系良好</v>
+        <v>冲突或孤立反复发生且修复无效</v>
       </c>
       <c r="I5" t="str">
-        <v>&lt;=2 分：关系紧张</v>
-      </c>
-      <c r="J5" t="str">
-        <v>3.0</v>
-      </c>
-      <c r="K5" t="str">
-        <v>0.85</v>
+        <v>同伴关系稳定</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B6" t="str">
-        <v>SELF_ESTEEM</v>
+        <v>SC_ADAPT</v>
       </c>
       <c r="C6" t="str">
-        <v>自尊水平</v>
+        <v>适应状况</v>
       </c>
       <c r="D6" t="str">
-        <v>q5</v>
+        <v>adp1,adp2,adp3</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1576,33 +1617,27 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>评估学生的自我价值感</v>
+        <v>适应状况维度</v>
       </c>
       <c r="H6" t="str">
-        <v>&gt;=4 分：自尊良好</v>
+        <v>出现拒学、躯体化且持续四周以上</v>
       </c>
       <c r="I6" t="str">
-        <v>&lt;=2 分：自尊低下</v>
-      </c>
-      <c r="J6" t="str">
-        <v>2.7</v>
-      </c>
-      <c r="K6" t="str">
-        <v>0.95</v>
+        <v>适应良好</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ST_QUICK</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B7" t="str">
-        <v>EMOTION</v>
+        <v>SC_TRIGGER</v>
       </c>
       <c r="C7" t="str">
-        <v>情绪问题</v>
+        <v>诱因清晰度</v>
       </c>
       <c r="D7" t="str">
-        <v>q1</v>
+        <v>ob1,ob2</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1611,33 +1646,27 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>评估学生情绪困扰程度</v>
+        <v>诱因清晰度维度</v>
       </c>
       <c r="H7" t="str">
-        <v>&gt;=4 分：情绪困扰严重</v>
+        <v>诱因不明确，行为难以预防</v>
       </c>
       <c r="I7" t="str">
-        <v>&lt;=2 分：情绪稳定</v>
-      </c>
-      <c r="J7" t="str">
-        <v>2.5</v>
-      </c>
-      <c r="K7" t="str">
-        <v>1.0</v>
+        <v>诱因清晰可干预</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ST_QUICK</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B8" t="str">
-        <v>BEHAVIOR</v>
+        <v>SC_FUNCTION</v>
       </c>
       <c r="C8" t="str">
-        <v>行为问题</v>
+        <v>功能影响</v>
       </c>
       <c r="D8" t="str">
-        <v>q2</v>
+        <v>ob3,ob4</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -1646,33 +1675,27 @@
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v>评估学生问题行为频率和严重度</v>
+        <v>功能影响维度</v>
       </c>
       <c r="H8" t="str">
-        <v>&gt;=4 分：行为问题突出</v>
+        <v>已明显影响学习与生活功能</v>
       </c>
       <c r="I8" t="str">
-        <v>&lt;=2 分：行为规范</v>
-      </c>
-      <c r="J8" t="str">
-        <v>2.3</v>
-      </c>
-      <c r="K8" t="str">
-        <v>1.05</v>
+        <v>功能影响有限</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ST_QUICK</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B9" t="str">
-        <v>MOTIVATION</v>
+        <v>SC_SUPPORT_TRIED</v>
       </c>
       <c r="C9" t="str">
-        <v>学习动机</v>
+        <v>既有支持有效性</v>
       </c>
       <c r="D9" t="str">
-        <v>q3</v>
+        <v>ob5,ob6</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>
@@ -1681,94 +1704,18 @@
         <v>1</v>
       </c>
       <c r="G9" t="str">
-        <v>评估学生学习的内外在动机</v>
+        <v>既有支持有效性维度</v>
       </c>
       <c r="H9" t="str">
-        <v>&gt;=4 分：动机强烈</v>
+        <v>已尝试的支持基本无效</v>
       </c>
       <c r="I9" t="str">
-        <v>&lt;=2 分：动机缺失</v>
-      </c>
-      <c r="J9" t="str">
-        <v>2.9</v>
-      </c>
-      <c r="K9" t="str">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>ST_QUICK</v>
-      </c>
-      <c r="B10" t="str">
-        <v>RELATION</v>
-      </c>
-      <c r="C10" t="str">
-        <v>人际关系</v>
-      </c>
-      <c r="D10" t="str">
-        <v>q4</v>
-      </c>
-      <c r="E10" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F10" t="str">
-        <v>1</v>
-      </c>
-      <c r="G10" t="str">
-        <v>评估学生与同伴和教师的关系质量</v>
-      </c>
-      <c r="H10" t="str">
-        <v>&gt;=4 分：关系良好</v>
-      </c>
-      <c r="I10" t="str">
-        <v>&lt;=2 分：关系紧张</v>
-      </c>
-      <c r="J10" t="str">
-        <v>3.0</v>
-      </c>
-      <c r="K10" t="str">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>ST_QUICK</v>
-      </c>
-      <c r="B11" t="str">
-        <v>SELF_ESTEEM</v>
-      </c>
-      <c r="C11" t="str">
-        <v>自尊水平</v>
-      </c>
-      <c r="D11" t="str">
-        <v>q5</v>
-      </c>
-      <c r="E11" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F11" t="str">
-        <v>1</v>
-      </c>
-      <c r="G11" t="str">
-        <v>评估学生的自我价值感</v>
-      </c>
-      <c r="H11" t="str">
-        <v>&gt;=4 分：自尊良好</v>
-      </c>
-      <c r="I11" t="str">
-        <v>&lt;=2 分：自尊低下</v>
-      </c>
-      <c r="J11" t="str">
-        <v>2.7</v>
-      </c>
-      <c r="K11" t="str">
-        <v>0.95</v>
+        <v>既有支持有效</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/student_case/assessment.xlsx
+++ b/business-libraries/test-data/student_case/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:V3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,21 +437,36 @@
         <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
+        <v>量表角色*</v>
+      </c>
+      <c r="M1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="N1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="O1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="P1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="Q1" t="str">
         <v>结果可见性*</v>
       </c>
-      <c r="M1" t="str">
+      <c r="R1" t="str">
         <v>数据敏感级*</v>
       </c>
-      <c r="N1" t="str">
+      <c r="S1" t="str">
         <v>来源属性*</v>
       </c>
-      <c r="O1" t="str">
+      <c r="T1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="P1" t="str">
+      <c r="U1" t="str">
         <v>版本*</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="V1" t="str">
         <v>量表说明</v>
       </c>
     </row>
@@ -490,21 +505,36 @@
         <v>6</v>
       </c>
       <c r="L2" t="str">
+        <v>入口筛查</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="M2" t="str">
+      <c r="R2" t="str">
         <v>sensitive</v>
       </c>
-      <c r="N2" t="str">
+      <c r="S2" t="str">
         <v>proprietary</v>
       </c>
-      <c r="O2" t="str">
+      <c r="T2" t="str">
         <v>学生个体问题手册v1</v>
       </c>
-      <c r="P2" t="str">
+      <c r="U2" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="V2" t="str">
         <v>从学业、行为、情绪、社交和适应五类表现进行教育场景筛查，不构成医学诊断。</v>
       </c>
     </row>
@@ -543,27 +573,42 @@
         <v>8</v>
       </c>
       <c r="L3" t="str">
+        <v>深度诊断</v>
+      </c>
+      <c r="M3" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>量表[SC_FIVE_CAT].均分 &gt;= 3.2 或 量表[SC_FIVE_CAT].维度[SC_EMOTION] &gt;= 3.5</v>
+      </c>
+      <c r="P3" t="str">
+        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
+      </c>
+      <c r="Q3" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="M3" t="str">
+      <c r="R3" t="str">
         <v>sensitive</v>
       </c>
-      <c r="N3" t="str">
+      <c r="S3" t="str">
         <v>proprietary</v>
       </c>
-      <c r="O3" t="str">
+      <c r="T3" t="str">
         <v>学生个体问题手册v1</v>
       </c>
-      <c r="P3" t="str">
+      <c r="U3" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="V3" t="str">
         <v>在五类筛查提示需要深入了解后使用，按事件—行为—结果—诱因—已尝试支持做结构化观察。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/test-data/student_case/assessment.xlsx
+++ b/business-libraries/test-data/student_case/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:AL3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,55 +419,103 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
+        <v>适用年级</v>
+      </c>
+      <c r="G1" t="str">
+        <v>适用学科</v>
+      </c>
+      <c r="H1" t="str">
         <v>施测对象*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>施测形式*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>触发方式*</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>作答频次*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>是否必做*</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>预计用时分钟*</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>作答时限分钟</v>
+      </c>
+      <c r="O1" t="str">
+        <v>最低题数</v>
+      </c>
+      <c r="P1" t="str">
+        <v>使用时机</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>重评间隔天数</v>
+      </c>
+      <c r="R1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="S1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="T1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="U1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="V1" t="str">
+        <v>结果可见性*</v>
+      </c>
+      <c r="W1" t="str">
+        <v>责任角色</v>
+      </c>
+      <c r="X1" t="str">
+        <v>数据敏感级*</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>来源属性*</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>外部授权说明</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>手册出处*</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>版本*</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>量表说明</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>常模参照</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>信度说明</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>效度说明</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>适用前提</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>不适合情况</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>后续建议动作</v>
+      </c>
+      <c r="AK1" t="str">
         <v>量表角色*</v>
       </c>
-      <c r="M1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="N1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="O1" t="str">
-        <v>触发条件</v>
-      </c>
-      <c r="P1" t="str">
-        <v>触发条件说明</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="R1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="S1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="T1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="V1" t="str">
-        <v>量表说明</v>
+      <c r="AL1" t="str">
+        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
@@ -487,55 +535,103 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>teacher</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>self_report</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>manual</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>per_case</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>是</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>6</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>从学业、行为、情绪、社交和适应五类表现进行教育场景筛查，不构成医学诊断。</v>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
         <v>入口筛查</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T2" t="str">
-        <v>学生个体问题手册v1</v>
-      </c>
-      <c r="U2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V2" t="str">
-        <v>从学业、行为、情绪、社交和适应五类表现进行教育场景筛查，不构成医学诊断。</v>
+      <c r="AL2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -555,67 +651,115 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>teacher</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>self_report</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>manual</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>per_case</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>否</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>8</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>量表[SC_FIVE_CAT].均分 &gt;= 3.2 或 量表[SC_FIVE_CAT].维度[SC_EMOTION] &gt;= 3.5</v>
+      </c>
+      <c r="U3" t="str">
+        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
+      </c>
+      <c r="V3" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>在五类筛查提示需要深入了解后使用，按事件—行为—结果—诱因—已尝试支持做结构化观察。</v>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
         <v>深度诊断</v>
       </c>
-      <c r="M3" t="str">
-        <v>SC_FIVE_CAT</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v>量表[SC_FIVE_CAT].均分 &gt;= 3.2 或 量表[SC_FIVE_CAT].维度[SC_EMOTION] &gt;= 3.5</v>
-      </c>
-      <c r="P3" t="str">
-        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R3" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T3" t="str">
-        <v>学生个体问题手册v1</v>
-      </c>
-      <c r="U3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V3" t="str">
-        <v>在五类筛查提示需要深入了解后使用，按事件—行为—结果—诱因—已尝试支持做结构化观察。</v>
+      <c r="AL3" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:P22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -631,22 +775,40 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
+        <v>子维度</v>
+      </c>
+      <c r="F1" t="str">
         <v>题干*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>题干举例</v>
+      </c>
+      <c r="H1" t="str">
         <v>选项组编码*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>反向计分*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>权重</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>是否必答*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>显示条件</v>
+      </c>
+      <c r="M1" t="str">
         <v>数据用途*</v>
+      </c>
+      <c r="N1" t="str">
+        <v>答题提示</v>
+      </c>
+      <c r="O1" t="str">
+        <v>题目说明</v>
+      </c>
+      <c r="P1" t="str">
+        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
@@ -663,22 +825,40 @@
         <v>学业表现</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>学习表现近期出现持续且明显的下降。</v>
       </c>
-      <c r="F2" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I2" t="str">
         <v>否</v>
       </c>
-      <c r="H2" t="str">
-        <v>1</v>
-      </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
         <v>是</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>compute</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -695,22 +875,40 @@
         <v>学业表现</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>完成作业、听课或考试受到明显影响。</v>
       </c>
-      <c r="F3" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I3" t="str">
         <v>否</v>
       </c>
-      <c r="H3" t="str">
-        <v>1</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
         <v>是</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>compute</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -727,22 +925,40 @@
         <v>学业表现</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>已有常规支持措施没有带来改善。</v>
       </c>
-      <c r="F4" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I4" t="str">
         <v>否</v>
       </c>
-      <c r="H4" t="str">
-        <v>1</v>
-      </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
         <v>是</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>compute</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -759,22 +975,40 @@
         <v>行为表现</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>冲动、对抗或规则破坏行为频繁出现。</v>
       </c>
-      <c r="F5" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I5" t="str">
         <v>否</v>
       </c>
-      <c r="H5" t="str">
-        <v>1</v>
-      </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
         <v>是</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>compute</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -791,22 +1025,40 @@
         <v>行为表现</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>行为已经明显影响本人或同伴的学习。</v>
       </c>
-      <c r="F6" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I6" t="str">
         <v>否</v>
       </c>
-      <c r="H6" t="str">
-        <v>1</v>
-      </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
         <v>是</v>
       </c>
-      <c r="J6" t="str">
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>compute</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -823,22 +1075,40 @@
         <v>行为表现</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>行为发生的场景和诱因较难预测。</v>
       </c>
-      <c r="F7" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I7" t="str">
         <v>否</v>
       </c>
-      <c r="H7" t="str">
-        <v>1</v>
-      </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
         <v>是</v>
       </c>
-      <c r="J7" t="str">
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>compute</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -855,22 +1125,40 @@
         <v>情绪状态</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>持续出现低落、焦虑、易怒或明显退缩。</v>
       </c>
-      <c r="F8" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I8" t="str">
         <v>否</v>
       </c>
-      <c r="H8" t="str">
-        <v>1</v>
-      </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
         <v>是</v>
       </c>
-      <c r="J8" t="str">
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>compute</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -887,22 +1175,40 @@
         <v>情绪状态</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>情绪变化已经影响日常功能。</v>
       </c>
-      <c r="F9" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I9" t="str">
         <v>否</v>
       </c>
-      <c r="H9" t="str">
-        <v>1</v>
-      </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
         <v>是</v>
       </c>
-      <c r="J9" t="str">
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>compute</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -919,22 +1225,40 @@
         <v>情绪状态</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>学生很难表达或调节当前感受。</v>
       </c>
-      <c r="F10" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I10" t="str">
         <v>否</v>
       </c>
-      <c r="H10" t="str">
-        <v>1</v>
-      </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
         <v>是</v>
       </c>
-      <c r="J10" t="str">
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>compute</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -951,22 +1275,40 @@
         <v>同伴社交</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>与同伴的冲突、排斥或孤立反复发生。</v>
       </c>
-      <c r="F11" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I11" t="str">
         <v>否</v>
       </c>
-      <c r="H11" t="str">
-        <v>1</v>
-      </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
         <v>是</v>
       </c>
-      <c r="J11" t="str">
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>compute</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -983,22 +1325,40 @@
         <v>同伴社交</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>学生缺少稳定的同伴支持。</v>
       </c>
-      <c r="F12" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I12" t="str">
         <v>否</v>
       </c>
-      <c r="H12" t="str">
-        <v>1</v>
-      </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
         <v>是</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>compute</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1015,22 +1375,40 @@
         <v>同伴社交</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>常规关系修复方式效果有限。</v>
       </c>
-      <c r="F13" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I13" t="str">
         <v>否</v>
       </c>
-      <c r="H13" t="str">
-        <v>1</v>
-      </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
         <v>是</v>
       </c>
-      <c r="J13" t="str">
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>compute</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1047,22 +1425,40 @@
         <v>适应状况</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>在转班、家庭变化或重要事件后持续难以适应。</v>
       </c>
-      <c r="F14" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I14" t="str">
         <v>否</v>
       </c>
-      <c r="H14" t="str">
-        <v>1</v>
-      </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
         <v>是</v>
       </c>
-      <c r="J14" t="str">
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>compute</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1079,22 +1475,40 @@
         <v>适应状况</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>出现明显躯体不适、拒学或回避。</v>
       </c>
-      <c r="F15" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I15" t="str">
         <v>否</v>
       </c>
-      <c r="H15" t="str">
-        <v>1</v>
-      </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
         <v>是</v>
       </c>
-      <c r="J15" t="str">
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v>compute</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1111,22 +1525,40 @@
         <v>适应状况</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>问题持续四周以上且没有改善趋势。</v>
       </c>
-      <c r="F16" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I16" t="str">
         <v>否</v>
       </c>
-      <c r="H16" t="str">
-        <v>1</v>
-      </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
         <v>是</v>
       </c>
-      <c r="J16" t="str">
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>compute</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1143,22 +1575,40 @@
         <v>诱因清晰度</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>行为发生前的情境难以识别。</v>
       </c>
-      <c r="F17" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I17" t="str">
         <v>否</v>
       </c>
-      <c r="H17" t="str">
-        <v>1</v>
-      </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
         <v>是</v>
       </c>
-      <c r="J17" t="str">
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v>compute</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1175,22 +1625,40 @@
         <v>诱因清晰度</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
         <v>同样的情境下行为反应不一致。</v>
       </c>
-      <c r="F18" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I18" t="str">
         <v>否</v>
       </c>
-      <c r="H18" t="str">
-        <v>1</v>
-      </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
         <v>是</v>
       </c>
-      <c r="J18" t="str">
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <v>compute</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1207,22 +1675,40 @@
         <v>功能影响</v>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
         <v>该表现已影响学生完成日常学习任务。</v>
       </c>
-      <c r="F19" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I19" t="str">
         <v>否</v>
       </c>
-      <c r="H19" t="str">
-        <v>1</v>
-      </c>
-      <c r="I19" t="str">
+      <c r="J19" t="str">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
         <v>是</v>
       </c>
-      <c r="J19" t="str">
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
         <v>compute</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1239,22 +1725,40 @@
         <v>功能影响</v>
       </c>
       <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
         <v>该表现已影响学生与他人的正常互动。</v>
       </c>
-      <c r="F20" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I20" t="str">
         <v>否</v>
       </c>
-      <c r="H20" t="str">
-        <v>1</v>
-      </c>
-      <c r="I20" t="str">
+      <c r="J20" t="str">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
         <v>是</v>
       </c>
-      <c r="J20" t="str">
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
         <v>compute</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1271,22 +1775,40 @@
         <v>既有支持有效性</v>
       </c>
       <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
         <v>已尝试的座位调整、谈话等措施没有带来改善。</v>
       </c>
-      <c r="F21" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I21" t="str">
         <v>否</v>
       </c>
-      <c r="H21" t="str">
-        <v>1</v>
-      </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
         <v>是</v>
       </c>
-      <c r="J21" t="str">
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
         <v>compute</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1303,27 +1825,45 @@
         <v>既有支持有效性</v>
       </c>
       <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
         <v>家庭配合的支持措施没有带来改善。</v>
       </c>
-      <c r="F22" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I22" t="str">
         <v>否</v>
       </c>
-      <c r="H22" t="str">
-        <v>1</v>
-      </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
+        <v>1</v>
+      </c>
+      <c r="K22" t="str">
         <v>是</v>
       </c>
-      <c r="J22" t="str">
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
         <v>compute</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P22"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1495,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1525,6 +2065,12 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
+      <c r="J1" t="str">
+        <v>常模均值</v>
+      </c>
+      <c r="K1" t="str">
+        <v>常模标准差</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1554,6 +2100,12 @@
       <c r="I2" t="str">
         <v>学业表现稳定</v>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1583,6 +2135,12 @@
       <c r="I3" t="str">
         <v>行为表现可控</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1612,6 +2170,12 @@
       <c r="I4" t="str">
         <v>情绪状态平稳</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1641,6 +2205,12 @@
       <c r="I5" t="str">
         <v>同伴关系稳定</v>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1670,6 +2240,12 @@
       <c r="I6" t="str">
         <v>适应良好</v>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1699,6 +2275,12 @@
       <c r="I7" t="str">
         <v>诱因清晰可干预</v>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -1728,6 +2310,12 @@
       <c r="I8" t="str">
         <v>功能影响有限</v>
       </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1757,10 +2345,16 @@
       <c r="I9" t="str">
         <v>既有支持有效</v>
       </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/student_case/assessment.xlsx
+++ b/business-libraries/test-data/student_case/assessment.xlsx
@@ -520,7 +520,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B2" t="str">
         <v>学生个体问题快速筛查</v>
@@ -586,7 +586,7 @@
         <v>teacher_only</v>
       </c>
       <c r="W2" t="str">
-        <v/>
+        <v>班主任</v>
       </c>
       <c r="X2" t="str">
         <v>sensitive</v>
@@ -601,7 +601,7 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AB2" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AC2" t="str">
         <v>从学业、行为、情绪、社交和适应五类表现进行教育场景筛查，不构成医学诊断。</v>
@@ -631,12 +631,12 @@
         <v>入口筛查</v>
       </c>
       <c r="AL2" t="str">
-        <v/>
+        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B3" t="str">
         <v>EBRCA 结构化观察记录</v>
@@ -687,13 +687,13 @@
         <v/>
       </c>
       <c r="R3" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="S3" t="str">
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>量表[SC_FIVE_CAT].均分 &gt;= 3.2 或 量表[SC_FIVE_CAT].维度[SC_EMOTION] &gt;= 3.5</v>
+        <v>量表[SC_S1].均分 &gt;= 3.2 或 量表[SC_S1].维度[SC_S1D3] &gt;= 3.5</v>
       </c>
       <c r="U3" t="str">
         <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
@@ -702,7 +702,7 @@
         <v>teacher_only</v>
       </c>
       <c r="W3" t="str">
-        <v/>
+        <v>班主任</v>
       </c>
       <c r="X3" t="str">
         <v>sensitive</v>
@@ -717,10 +717,10 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AB3" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AC3" t="str">
-        <v>在五类筛查提示需要深入了解后使用，按事件—行为—结果—诱因—已尝试支持做结构化观察。</v>
+        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -747,7 +747,7 @@
         <v>深度诊断</v>
       </c>
       <c r="AL3" t="str">
-        <v/>
+        <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
   </sheetData>
@@ -813,10 +813,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>aca1</v>
+        <v>q1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>aca2</v>
+        <v>q2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>aca3</v>
+        <v>q3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
@@ -963,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>beh1</v>
+        <v>q4</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>beh2</v>
+        <v>q5</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B7" t="str">
-        <v>beh3</v>
+        <v>q6</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B8" t="str">
-        <v>emo1</v>
+        <v>q7</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
@@ -1163,10 +1163,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B9" t="str">
-        <v>emo2</v>
+        <v>q8</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B10" t="str">
-        <v>emo3</v>
+        <v>q9</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
@@ -1263,10 +1263,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B11" t="str">
-        <v>soc1</v>
+        <v>q10</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B12" t="str">
-        <v>soc2</v>
+        <v>q11</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B13" t="str">
-        <v>soc3</v>
+        <v>q12</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B14" t="str">
-        <v>adp1</v>
+        <v>q13</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B15" t="str">
-        <v>adp2</v>
+        <v>q14</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B16" t="str">
-        <v>adp3</v>
+        <v>q15</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B17" t="str">
-        <v>ob1</v>
+        <v>q1</v>
       </c>
       <c r="C17" t="str">
         <v>single</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B18" t="str">
-        <v>ob2</v>
+        <v>q2</v>
       </c>
       <c r="C18" t="str">
         <v>single</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B19" t="str">
-        <v>ob3</v>
+        <v>q3</v>
       </c>
       <c r="C19" t="str">
         <v>single</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B20" t="str">
-        <v>ob4</v>
+        <v>q4</v>
       </c>
       <c r="C20" t="str">
         <v>single</v>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B21" t="str">
-        <v>ob5</v>
+        <v>q5</v>
       </c>
       <c r="C21" t="str">
         <v>single</v>
@@ -1813,10 +1813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B22" t="str">
-        <v>ob6</v>
+        <v>q6</v>
       </c>
       <c r="C22" t="str">
         <v>single</v>
@@ -1870,7 +1870,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1888,13 +1888,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>几乎没有</v>
+        <v>完全不符合</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1902,13 +1902,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>很少</v>
+        <v>比较不符合</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1916,13 +1916,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>有时</v>
+        <v>一般</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1930,13 +1930,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>经常</v>
+        <v>比较符合</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1944,91 +1944,21 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>几乎每天</v>
+        <v>非常符合</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B7" t="str">
-        <v>1</v>
-      </c>
-      <c r="C7" t="str">
-        <v>完全不符合</v>
-      </c>
-      <c r="D7" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2</v>
-      </c>
-      <c r="C8" t="str">
-        <v>比较不符合</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B9" t="str">
-        <v>3</v>
-      </c>
-      <c r="C9" t="str">
-        <v>一般</v>
-      </c>
-      <c r="D9" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B10" t="str">
-        <v>4</v>
-      </c>
-      <c r="C10" t="str">
-        <v>比较符合</v>
-      </c>
-      <c r="D10" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B11" t="str">
-        <v>5</v>
-      </c>
-      <c r="C11" t="str">
-        <v>非常符合</v>
-      </c>
-      <c r="D11" t="str">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2074,16 +2004,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>SC_ACADEMIC</v>
+        <v>SC_S1D1</v>
       </c>
       <c r="C2" t="str">
         <v>学业表现</v>
       </c>
       <c r="D2" t="str">
-        <v>aca1,aca2,aca3</v>
+        <v>q1,q2,q3</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -2109,16 +2039,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>SC_BEHAVIOR</v>
+        <v>SC_S1D2</v>
       </c>
       <c r="C3" t="str">
         <v>行为表现</v>
       </c>
       <c r="D3" t="str">
-        <v>beh1,beh2,beh3</v>
+        <v>q4,q5,q6</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -2144,16 +2074,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>SC_EMOTION</v>
+        <v>SC_S1D3</v>
       </c>
       <c r="C4" t="str">
         <v>情绪状态</v>
       </c>
       <c r="D4" t="str">
-        <v>emo1,emo2,emo3</v>
+        <v>q7,q8,q9</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -2179,16 +2109,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>SC_SOCIAL</v>
+        <v>SC_S1D4</v>
       </c>
       <c r="C5" t="str">
         <v>同伴社交</v>
       </c>
       <c r="D5" t="str">
-        <v>soc1,soc2,soc3</v>
+        <v>q10,q11,q12</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -2214,16 +2144,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>SC_ADAPT</v>
+        <v>SC_S1D5</v>
       </c>
       <c r="C6" t="str">
         <v>适应状况</v>
       </c>
       <c r="D6" t="str">
-        <v>adp1,adp2,adp3</v>
+        <v>q13,q14,q15</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -2249,16 +2179,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>SC_TRIGGER</v>
+        <v>SC_S2D1</v>
       </c>
       <c r="C7" t="str">
         <v>诱因清晰度</v>
       </c>
       <c r="D7" t="str">
-        <v>ob1,ob2</v>
+        <v>q1,q2</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -2284,16 +2214,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B8" t="str">
-        <v>SC_FUNCTION</v>
+        <v>SC_S2D2</v>
       </c>
       <c r="C8" t="str">
         <v>功能影响</v>
       </c>
       <c r="D8" t="str">
-        <v>ob3,ob4</v>
+        <v>q3,q4</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -2319,16 +2249,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B9" t="str">
-        <v>SC_SUPPORT_TRIED</v>
+        <v>SC_S2D3</v>
       </c>
       <c r="C9" t="str">
         <v>既有支持有效性</v>
       </c>
       <c r="D9" t="str">
-        <v>ob5,ob6</v>
+        <v>q5,q6</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>

--- a/business-libraries/test-data/student_case/assessment.xlsx
+++ b/business-libraries/test-data/student_case/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:V3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,108 +419,60 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
-        <v>适用年级</v>
+        <v>施测对象*</v>
       </c>
       <c r="G1" t="str">
-        <v>适用学科</v>
+        <v>施测形式*</v>
       </c>
       <c r="H1" t="str">
-        <v>施测对象*</v>
+        <v>触发方式*</v>
       </c>
       <c r="I1" t="str">
-        <v>施测形式*</v>
+        <v>作答频次*</v>
       </c>
       <c r="J1" t="str">
-        <v>触发方式*</v>
+        <v>是否必做*</v>
       </c>
       <c r="K1" t="str">
-        <v>作答频次*</v>
+        <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
-        <v>是否必做*</v>
+        <v>量表角色*</v>
       </c>
       <c r="M1" t="str">
-        <v>预计用时分钟*</v>
+        <v>前置量表编码</v>
       </c>
       <c r="N1" t="str">
-        <v>作答时限分钟</v>
+        <v>互斥量表编码</v>
       </c>
       <c r="O1" t="str">
-        <v>最低题数</v>
+        <v>触发条件</v>
       </c>
       <c r="P1" t="str">
-        <v>使用时机</v>
+        <v>触发条件说明</v>
       </c>
       <c r="Q1" t="str">
-        <v>重评间隔天数</v>
+        <v>结果可见性*</v>
       </c>
       <c r="R1" t="str">
-        <v>前置量表编码</v>
+        <v>数据敏感级*</v>
       </c>
       <c r="S1" t="str">
-        <v>互斥量表编码</v>
+        <v>来源属性*</v>
       </c>
       <c r="T1" t="str">
-        <v>触发条件</v>
+        <v>手册出处*</v>
       </c>
       <c r="U1" t="str">
-        <v>触发条件说明</v>
+        <v>版本*</v>
       </c>
       <c r="V1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="W1" t="str">
-        <v>责任角色</v>
-      </c>
-      <c r="X1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>外部授权说明</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="AC1" t="str">
         <v>量表说明</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>常模参照</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>信度说明</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>效度说明</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>隐私声明</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>适用前提</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>不适合情况</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>后续建议动作</v>
-      </c>
-      <c r="AK1" t="str">
-        <v>量表角色*</v>
-      </c>
-      <c r="AL1" t="str">
-        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B2" t="str">
         <v>学生个体问题快速筛查</v>
@@ -535,28 +487,28 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="G2" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="H2" t="str">
+        <v>manual</v>
+      </c>
+      <c r="I2" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="J2" t="str">
+        <v>是</v>
+      </c>
+      <c r="K2" t="str">
+        <v>6</v>
+      </c>
+      <c r="L2" t="str">
+        <v>入口筛查</v>
+      </c>
+      <c r="M2" t="str">
         <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v>teacher</v>
-      </c>
-      <c r="I2" t="str">
-        <v>self_report</v>
-      </c>
-      <c r="J2" t="str">
-        <v>manual</v>
-      </c>
-      <c r="K2" t="str">
-        <v>per_case</v>
-      </c>
-      <c r="L2" t="str">
-        <v>是</v>
-      </c>
-      <c r="M2" t="str">
-        <v>6</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -568,75 +520,27 @@
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>teacher_only</v>
       </c>
       <c r="R2" t="str">
-        <v/>
+        <v>sensitive</v>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>学生个体问题手册v1</v>
       </c>
       <c r="U2" t="str">
-        <v/>
+        <v>1.0.0</v>
       </c>
       <c r="V2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="W2" t="str">
-        <v>班主任</v>
-      </c>
-      <c r="X2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="Y2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="Z2" t="str">
-        <v/>
-      </c>
-      <c r="AA2" t="str">
-        <v>学生个体问题手册v1</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>4.0.0</v>
-      </c>
-      <c r="AC2" t="str">
         <v>从学业、行为、情绪、社交和适应五类表现进行教育场景筛查，不构成医学诊断。</v>
-      </c>
-      <c r="AD2" t="str">
-        <v/>
-      </c>
-      <c r="AE2" t="str">
-        <v/>
-      </c>
-      <c r="AF2" t="str">
-        <v/>
-      </c>
-      <c r="AG2" t="str">
-        <v/>
-      </c>
-      <c r="AH2" t="str">
-        <v/>
-      </c>
-      <c r="AI2" t="str">
-        <v/>
-      </c>
-      <c r="AJ2" t="str">
-        <v/>
-      </c>
-      <c r="AK2" t="str">
-        <v>入口筛查</v>
-      </c>
-      <c r="AL2" t="str">
-        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B3" t="str">
         <v>EBRCA 结构化观察记录</v>
@@ -651,115 +555,67 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H3" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I3" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J3" t="str">
-        <v>manual</v>
+        <v>否</v>
       </c>
       <c r="K3" t="str">
-        <v>per_case</v>
+        <v>8</v>
       </c>
       <c r="L3" t="str">
-        <v>否</v>
+        <v>深度诊断</v>
       </c>
       <c r="M3" t="str">
-        <v>8</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="N3" t="str">
         <v/>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>量表[SC_FIVE_CAT].均分 &gt;= 3.2 或 量表[SC_FIVE_CAT].维度[SC_EMOTION] &gt;= 3.5</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>teacher_only</v>
       </c>
       <c r="R3" t="str">
-        <v>SC_S1</v>
+        <v>sensitive</v>
       </c>
       <c r="S3" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="T3" t="str">
-        <v>量表[SC_S1].均分 &gt;= 3.2 或 量表[SC_S1].维度[SC_S1D3] &gt;= 3.5</v>
+        <v>学生个体问题手册v1</v>
       </c>
       <c r="U3" t="str">
-        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
+        <v>1.0.0</v>
       </c>
       <c r="V3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="W3" t="str">
-        <v>班主任</v>
-      </c>
-      <c r="X3" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="Y3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="Z3" t="str">
-        <v/>
-      </c>
-      <c r="AA3" t="str">
-        <v>学生个体问题手册v1</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>4.0.0</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
-      </c>
-      <c r="AD3" t="str">
-        <v/>
-      </c>
-      <c r="AE3" t="str">
-        <v/>
-      </c>
-      <c r="AF3" t="str">
-        <v/>
-      </c>
-      <c r="AG3" t="str">
-        <v/>
-      </c>
-      <c r="AH3" t="str">
-        <v/>
-      </c>
-      <c r="AI3" t="str">
-        <v/>
-      </c>
-      <c r="AJ3" t="str">
-        <v/>
-      </c>
-      <c r="AK3" t="str">
-        <v>深度诊断</v>
-      </c>
-      <c r="AL3" t="str">
-        <v>定位薄弱维度，匹配对应工具</v>
+        <v>在五类筛查提示需要深入了解后使用，按事件—行为—结果—诱因—已尝试支持做结构化观察。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:J22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -775,48 +631,30 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
-        <v>子维度</v>
+        <v>题干*</v>
       </c>
       <c r="F1" t="str">
-        <v>题干*</v>
+        <v>选项组编码*</v>
       </c>
       <c r="G1" t="str">
-        <v>题干举例</v>
+        <v>反向计分*</v>
       </c>
       <c r="H1" t="str">
-        <v>选项组编码*</v>
+        <v>权重</v>
       </c>
       <c r="I1" t="str">
-        <v>反向计分*</v>
+        <v>是否必答*</v>
       </c>
       <c r="J1" t="str">
-        <v>权重</v>
-      </c>
-      <c r="K1" t="str">
-        <v>是否必答*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>显示条件</v>
-      </c>
-      <c r="M1" t="str">
         <v>数据用途*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>答题提示</v>
-      </c>
-      <c r="O1" t="str">
-        <v>题目说明</v>
-      </c>
-      <c r="P1" t="str">
-        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B2" t="str">
-        <v>q1</v>
+        <v>aca1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
@@ -825,48 +663,30 @@
         <v>学业表现</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>学习表现近期出现持续且明显的下降。</v>
       </c>
       <c r="F2" t="str">
-        <v>学习表现近期出现持续且明显的下降。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H2" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>1</v>
-      </c>
-      <c r="K2" t="str">
-        <v>是</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B3" t="str">
-        <v>q2</v>
+        <v>aca2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
@@ -875,48 +695,30 @@
         <v>学业表现</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>完成作业、听课或考试受到明显影响。</v>
       </c>
       <c r="F3" t="str">
-        <v>完成作业、听课或考试受到明显影响。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H3" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J3" t="str">
-        <v>1</v>
-      </c>
-      <c r="K3" t="str">
-        <v>是</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B4" t="str">
-        <v>q3</v>
+        <v>aca3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
@@ -925,48 +727,30 @@
         <v>学业表现</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>已有常规支持措施没有带来改善。</v>
       </c>
       <c r="F4" t="str">
-        <v>已有常规支持措施没有带来改善。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H4" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J4" t="str">
-        <v>1</v>
-      </c>
-      <c r="K4" t="str">
-        <v>是</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B5" t="str">
-        <v>q4</v>
+        <v>beh1</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
@@ -975,48 +759,30 @@
         <v>行为表现</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>冲动、对抗或规则破坏行为频繁出现。</v>
       </c>
       <c r="F5" t="str">
-        <v>冲动、对抗或规则破坏行为频繁出现。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H5" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J5" t="str">
-        <v>1</v>
-      </c>
-      <c r="K5" t="str">
-        <v>是</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B6" t="str">
-        <v>q5</v>
+        <v>beh2</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
@@ -1025,48 +791,30 @@
         <v>行为表现</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>行为已经明显影响本人或同伴的学习。</v>
       </c>
       <c r="F6" t="str">
-        <v>行为已经明显影响本人或同伴的学习。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H6" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J6" t="str">
-        <v>1</v>
-      </c>
-      <c r="K6" t="str">
-        <v>是</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B7" t="str">
-        <v>q6</v>
+        <v>beh3</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
@@ -1075,48 +823,30 @@
         <v>行为表现</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>行为发生的场景和诱因较难预测。</v>
       </c>
       <c r="F7" t="str">
-        <v>行为发生的场景和诱因较难预测。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H7" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J7" t="str">
-        <v>1</v>
-      </c>
-      <c r="K7" t="str">
-        <v>是</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B8" t="str">
-        <v>q7</v>
+        <v>emo1</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
@@ -1125,48 +855,30 @@
         <v>情绪状态</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>持续出现低落、焦虑、易怒或明显退缩。</v>
       </c>
       <c r="F8" t="str">
-        <v>持续出现低落、焦虑、易怒或明显退缩。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H8" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J8" t="str">
-        <v>1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>是</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B9" t="str">
-        <v>q8</v>
+        <v>emo2</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
@@ -1175,48 +887,30 @@
         <v>情绪状态</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>情绪变化已经影响日常功能。</v>
       </c>
       <c r="F9" t="str">
-        <v>情绪变化已经影响日常功能。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H9" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J9" t="str">
-        <v>1</v>
-      </c>
-      <c r="K9" t="str">
-        <v>是</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B10" t="str">
-        <v>q9</v>
+        <v>emo3</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
@@ -1225,48 +919,30 @@
         <v>情绪状态</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>学生很难表达或调节当前感受。</v>
       </c>
       <c r="F10" t="str">
-        <v>学生很难表达或调节当前感受。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H10" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J10" t="str">
-        <v>1</v>
-      </c>
-      <c r="K10" t="str">
-        <v>是</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B11" t="str">
-        <v>q10</v>
+        <v>soc1</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
@@ -1275,48 +951,30 @@
         <v>同伴社交</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>与同伴的冲突、排斥或孤立反复发生。</v>
       </c>
       <c r="F11" t="str">
-        <v>与同伴的冲突、排斥或孤立反复发生。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H11" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J11" t="str">
-        <v>1</v>
-      </c>
-      <c r="K11" t="str">
-        <v>是</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B12" t="str">
-        <v>q11</v>
+        <v>soc2</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
@@ -1325,48 +983,30 @@
         <v>同伴社交</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>学生缺少稳定的同伴支持。</v>
       </c>
       <c r="F12" t="str">
-        <v>学生缺少稳定的同伴支持。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H12" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I12" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J12" t="str">
-        <v>1</v>
-      </c>
-      <c r="K12" t="str">
-        <v>是</v>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B13" t="str">
-        <v>q12</v>
+        <v>soc3</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
@@ -1375,48 +1015,30 @@
         <v>同伴社交</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>常规关系修复方式效果有限。</v>
       </c>
       <c r="F13" t="str">
-        <v>常规关系修复方式效果有限。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H13" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I13" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J13" t="str">
-        <v>1</v>
-      </c>
-      <c r="K13" t="str">
-        <v>是</v>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B14" t="str">
-        <v>q13</v>
+        <v>adp1</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1425,48 +1047,30 @@
         <v>适应状况</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>在转班、家庭变化或重要事件后持续难以适应。</v>
       </c>
       <c r="F14" t="str">
-        <v>在转班、家庭变化或重要事件后持续难以适应。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H14" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I14" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J14" t="str">
-        <v>1</v>
-      </c>
-      <c r="K14" t="str">
-        <v>是</v>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-      <c r="P14" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B15" t="str">
-        <v>q14</v>
+        <v>adp2</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
@@ -1475,48 +1079,30 @@
         <v>适应状况</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>出现明显躯体不适、拒学或回避。</v>
       </c>
       <c r="F15" t="str">
-        <v>出现明显躯体不适、拒学或回避。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H15" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I15" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J15" t="str">
-        <v>1</v>
-      </c>
-      <c r="K15" t="str">
-        <v>是</v>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B16" t="str">
-        <v>q15</v>
+        <v>adp3</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
@@ -1525,48 +1111,30 @@
         <v>适应状况</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>问题持续四周以上且没有改善趋势。</v>
       </c>
       <c r="F16" t="str">
-        <v>问题持续四周以上且没有改善趋势。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H16" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I16" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J16" t="str">
-        <v>1</v>
-      </c>
-      <c r="K16" t="str">
-        <v>是</v>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-      <c r="P16" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B17" t="str">
-        <v>q1</v>
+        <v>ob1</v>
       </c>
       <c r="C17" t="str">
         <v>single</v>
@@ -1575,48 +1143,30 @@
         <v>诱因清晰度</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>行为发生前的情境难以识别。</v>
       </c>
       <c r="F17" t="str">
-        <v>行为发生前的情境难以识别。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H17" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I17" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J17" t="str">
-        <v>1</v>
-      </c>
-      <c r="K17" t="str">
-        <v>是</v>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
-        <v/>
-      </c>
-      <c r="P17" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B18" t="str">
-        <v>q2</v>
+        <v>ob2</v>
       </c>
       <c r="C18" t="str">
         <v>single</v>
@@ -1625,48 +1175,30 @@
         <v>诱因清晰度</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>同样的情境下行为反应不一致。</v>
       </c>
       <c r="F18" t="str">
-        <v>同样的情境下行为反应不一致。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H18" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I18" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J18" t="str">
-        <v>1</v>
-      </c>
-      <c r="K18" t="str">
-        <v>是</v>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N18" t="str">
-        <v/>
-      </c>
-      <c r="O18" t="str">
-        <v/>
-      </c>
-      <c r="P18" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B19" t="str">
-        <v>q3</v>
+        <v>ob3</v>
       </c>
       <c r="C19" t="str">
         <v>single</v>
@@ -1675,48 +1207,30 @@
         <v>功能影响</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>该表现已影响学生完成日常学习任务。</v>
       </c>
       <c r="F19" t="str">
-        <v>该表现已影响学生完成日常学习任务。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H19" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I19" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J19" t="str">
-        <v>1</v>
-      </c>
-      <c r="K19" t="str">
-        <v>是</v>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
-        <v/>
-      </c>
-      <c r="P19" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B20" t="str">
-        <v>q4</v>
+        <v>ob4</v>
       </c>
       <c r="C20" t="str">
         <v>single</v>
@@ -1725,48 +1239,30 @@
         <v>功能影响</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>该表现已影响学生与他人的正常互动。</v>
       </c>
       <c r="F20" t="str">
-        <v>该表现已影响学生与他人的正常互动。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H20" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I20" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J20" t="str">
-        <v>1</v>
-      </c>
-      <c r="K20" t="str">
-        <v>是</v>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N20" t="str">
-        <v/>
-      </c>
-      <c r="O20" t="str">
-        <v/>
-      </c>
-      <c r="P20" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B21" t="str">
-        <v>q5</v>
+        <v>ob5</v>
       </c>
       <c r="C21" t="str">
         <v>single</v>
@@ -1775,48 +1271,30 @@
         <v>既有支持有效性</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>已尝试的座位调整、谈话等措施没有带来改善。</v>
       </c>
       <c r="F21" t="str">
-        <v>已尝试的座位调整、谈话等措施没有带来改善。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H21" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I21" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J21" t="str">
-        <v>1</v>
-      </c>
-      <c r="K21" t="str">
-        <v>是</v>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="M21" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
-        <v/>
-      </c>
-      <c r="P21" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B22" t="str">
-        <v>q6</v>
+        <v>ob6</v>
       </c>
       <c r="C22" t="str">
         <v>single</v>
@@ -1825,52 +1303,34 @@
         <v>既有支持有效性</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>家庭配合的支持措施没有带来改善。</v>
       </c>
       <c r="F22" t="str">
-        <v>家庭配合的支持措施没有带来改善。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H22" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I22" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J22" t="str">
-        <v>1</v>
-      </c>
-      <c r="K22" t="str">
-        <v>是</v>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N22" t="str">
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-      <c r="P22" t="str">
-        <v/>
+        <v>compute</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1888,13 +1348,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>完全不符合</v>
+        <v>几乎没有</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1902,13 +1362,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>比较不符合</v>
+        <v>很少</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1916,13 +1376,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>一般</v>
+        <v>有时</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1930,13 +1390,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>比较符合</v>
+        <v>经常</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1944,28 +1404,98 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>非常符合</v>
+        <v>几乎每天</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>3</v>
+      </c>
+      <c r="C9" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D9" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>4</v>
+      </c>
+      <c r="C10" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B11" t="str">
+        <v>5</v>
+      </c>
+      <c r="C11" t="str">
+        <v>非常符合</v>
+      </c>
+      <c r="D11" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:I9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1995,25 +1525,19 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
-      <c r="J1" t="str">
-        <v>常模均值</v>
-      </c>
-      <c r="K1" t="str">
-        <v>常模标准差</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B2" t="str">
-        <v>SC_S1D1</v>
+        <v>SC_ACADEMIC</v>
       </c>
       <c r="C2" t="str">
         <v>学业表现</v>
       </c>
       <c r="D2" t="str">
-        <v>q1,q2,q3</v>
+        <v>aca1,aca2,aca3</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -2030,25 +1554,19 @@
       <c r="I2" t="str">
         <v>学业表现稳定</v>
       </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B3" t="str">
-        <v>SC_S1D2</v>
+        <v>SC_BEHAVIOR</v>
       </c>
       <c r="C3" t="str">
         <v>行为表现</v>
       </c>
       <c r="D3" t="str">
-        <v>q4,q5,q6</v>
+        <v>beh1,beh2,beh3</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -2065,25 +1583,19 @@
       <c r="I3" t="str">
         <v>行为表现可控</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B4" t="str">
-        <v>SC_S1D3</v>
+        <v>SC_EMOTION</v>
       </c>
       <c r="C4" t="str">
         <v>情绪状态</v>
       </c>
       <c r="D4" t="str">
-        <v>q7,q8,q9</v>
+        <v>emo1,emo2,emo3</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -2100,25 +1612,19 @@
       <c r="I4" t="str">
         <v>情绪状态平稳</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B5" t="str">
-        <v>SC_S1D4</v>
+        <v>SC_SOCIAL</v>
       </c>
       <c r="C5" t="str">
         <v>同伴社交</v>
       </c>
       <c r="D5" t="str">
-        <v>q10,q11,q12</v>
+        <v>soc1,soc2,soc3</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -2135,25 +1641,19 @@
       <c r="I5" t="str">
         <v>同伴关系稳定</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="B6" t="str">
-        <v>SC_S1D5</v>
+        <v>SC_ADAPT</v>
       </c>
       <c r="C6" t="str">
         <v>适应状况</v>
       </c>
       <c r="D6" t="str">
-        <v>q13,q14,q15</v>
+        <v>adp1,adp2,adp3</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -2170,25 +1670,19 @@
       <c r="I6" t="str">
         <v>适应良好</v>
       </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B7" t="str">
-        <v>SC_S2D1</v>
+        <v>SC_TRIGGER</v>
       </c>
       <c r="C7" t="str">
         <v>诱因清晰度</v>
       </c>
       <c r="D7" t="str">
-        <v>q1,q2</v>
+        <v>ob1,ob2</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -2205,25 +1699,19 @@
       <c r="I7" t="str">
         <v>诱因清晰可干预</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B8" t="str">
-        <v>SC_S2D2</v>
+        <v>SC_FUNCTION</v>
       </c>
       <c r="C8" t="str">
         <v>功能影响</v>
       </c>
       <c r="D8" t="str">
-        <v>q3,q4</v>
+        <v>ob3,ob4</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -2240,25 +1728,19 @@
       <c r="I8" t="str">
         <v>功能影响有限</v>
       </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="B9" t="str">
-        <v>SC_S2D3</v>
+        <v>SC_SUPPORT_TRIED</v>
       </c>
       <c r="C9" t="str">
         <v>既有支持有效性</v>
       </c>
       <c r="D9" t="str">
-        <v>q5,q6</v>
+        <v>ob5,ob6</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>
@@ -2275,16 +1757,10 @@
       <c r="I9" t="str">
         <v>既有支持有效</v>
       </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/student_case/assessment.xlsx
+++ b/business-libraries/test-data/student_case/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:AL3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,60 +419,108 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
+        <v>适用年级</v>
+      </c>
+      <c r="G1" t="str">
+        <v>适用学科</v>
+      </c>
+      <c r="H1" t="str">
         <v>施测对象*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>施测形式*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>触发方式*</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>作答频次*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>是否必做*</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>预计用时分钟*</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>作答时限分钟</v>
+      </c>
+      <c r="O1" t="str">
+        <v>最低题数</v>
+      </c>
+      <c r="P1" t="str">
+        <v>使用时机</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>重评间隔天数</v>
+      </c>
+      <c r="R1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="S1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="T1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="U1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="V1" t="str">
+        <v>结果可见性*</v>
+      </c>
+      <c r="W1" t="str">
+        <v>责任角色</v>
+      </c>
+      <c r="X1" t="str">
+        <v>数据敏感级*</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>来源属性*</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>外部授权说明</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>手册出处*</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>版本*</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>量表说明</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>常模参照</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>信度说明</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>效度说明</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>适用前提</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>不适合情况</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>后续建议动作</v>
+      </c>
+      <c r="AK1" t="str">
         <v>量表角色*</v>
       </c>
-      <c r="M1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="N1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="O1" t="str">
-        <v>触发条件</v>
-      </c>
-      <c r="P1" t="str">
-        <v>触发条件说明</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="R1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="S1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="T1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="V1" t="str">
-        <v>量表说明</v>
+      <c r="AL1" t="str">
+        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B2" t="str">
         <v>学生个体问题快速筛查</v>
@@ -487,60 +535,108 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>teacher</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>self_report</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>manual</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>per_case</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>是</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>6</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W2" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X2" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>从学业、行为、情绪、社交和适应五类表现进行教育场景筛查，不构成医学诊断。</v>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
         <v>入口筛查</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T2" t="str">
-        <v>学生个体问题手册v1</v>
-      </c>
-      <c r="U2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V2" t="str">
-        <v>从学业、行为、情绪、社交和适应五类表现进行教育场景筛查，不构成医学诊断。</v>
+      <c r="AL2" t="str">
+        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B3" t="str">
         <v>EBRCA 结构化观察记录</v>
@@ -555,67 +651,115 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>teacher</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>self_report</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>manual</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>per_case</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>否</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>8</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>量表[SC_S1].均分 &gt;= 3.2 或 量表[SC_S1].维度[SC_S1D3] &gt;= 3.5</v>
+      </c>
+      <c r="U3" t="str">
+        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
+      </c>
+      <c r="V3" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W3" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X3" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
         <v>深度诊断</v>
       </c>
-      <c r="M3" t="str">
-        <v>SC_FIVE_CAT</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v>量表[SC_FIVE_CAT].均分 &gt;= 3.2 或 量表[SC_FIVE_CAT].维度[SC_EMOTION] &gt;= 3.5</v>
-      </c>
-      <c r="P3" t="str">
-        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R3" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T3" t="str">
-        <v>学生个体问题手册v1</v>
-      </c>
-      <c r="U3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V3" t="str">
-        <v>在五类筛查提示需要深入了解后使用，按事件—行为—结果—诱因—已尝试支持做结构化观察。</v>
+      <c r="AL3" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:P22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -631,30 +775,48 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
+        <v>子维度</v>
+      </c>
+      <c r="F1" t="str">
         <v>题干*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>题干举例</v>
+      </c>
+      <c r="H1" t="str">
         <v>选项组编码*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>反向计分*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>权重</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>是否必答*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>显示条件</v>
+      </c>
+      <c r="M1" t="str">
         <v>数据用途*</v>
+      </c>
+      <c r="N1" t="str">
+        <v>答题提示</v>
+      </c>
+      <c r="O1" t="str">
+        <v>题目说明</v>
+      </c>
+      <c r="P1" t="str">
+        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>aca1</v>
+        <v>q1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
@@ -663,30 +825,48 @@
         <v>学业表现</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>学习表现近期出现持续且明显的下降。</v>
       </c>
-      <c r="F2" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I2" t="str">
         <v>否</v>
       </c>
-      <c r="H2" t="str">
-        <v>1</v>
-      </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
         <v>是</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>compute</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>aca2</v>
+        <v>q2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
@@ -695,30 +875,48 @@
         <v>学业表现</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>完成作业、听课或考试受到明显影响。</v>
       </c>
-      <c r="F3" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I3" t="str">
         <v>否</v>
       </c>
-      <c r="H3" t="str">
-        <v>1</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
         <v>是</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>compute</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>aca3</v>
+        <v>q3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
@@ -727,30 +925,48 @@
         <v>学业表现</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>已有常规支持措施没有带来改善。</v>
       </c>
-      <c r="F4" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I4" t="str">
         <v>否</v>
       </c>
-      <c r="H4" t="str">
-        <v>1</v>
-      </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
         <v>是</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>compute</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>beh1</v>
+        <v>q4</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
@@ -759,30 +975,48 @@
         <v>行为表现</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>冲动、对抗或规则破坏行为频繁出现。</v>
       </c>
-      <c r="F5" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I5" t="str">
         <v>否</v>
       </c>
-      <c r="H5" t="str">
-        <v>1</v>
-      </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
         <v>是</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>compute</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>beh2</v>
+        <v>q5</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
@@ -791,30 +1025,48 @@
         <v>行为表现</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>行为已经明显影响本人或同伴的学习。</v>
       </c>
-      <c r="F6" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I6" t="str">
         <v>否</v>
       </c>
-      <c r="H6" t="str">
-        <v>1</v>
-      </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
         <v>是</v>
       </c>
-      <c r="J6" t="str">
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>compute</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B7" t="str">
-        <v>beh3</v>
+        <v>q6</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
@@ -823,30 +1075,48 @@
         <v>行为表现</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>行为发生的场景和诱因较难预测。</v>
       </c>
-      <c r="F7" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I7" t="str">
         <v>否</v>
       </c>
-      <c r="H7" t="str">
-        <v>1</v>
-      </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
         <v>是</v>
       </c>
-      <c r="J7" t="str">
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>compute</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B8" t="str">
-        <v>emo1</v>
+        <v>q7</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
@@ -855,30 +1125,48 @@
         <v>情绪状态</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>持续出现低落、焦虑、易怒或明显退缩。</v>
       </c>
-      <c r="F8" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I8" t="str">
         <v>否</v>
       </c>
-      <c r="H8" t="str">
-        <v>1</v>
-      </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
         <v>是</v>
       </c>
-      <c r="J8" t="str">
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>compute</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B9" t="str">
-        <v>emo2</v>
+        <v>q8</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
@@ -887,30 +1175,48 @@
         <v>情绪状态</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>情绪变化已经影响日常功能。</v>
       </c>
-      <c r="F9" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I9" t="str">
         <v>否</v>
       </c>
-      <c r="H9" t="str">
-        <v>1</v>
-      </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
         <v>是</v>
       </c>
-      <c r="J9" t="str">
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>compute</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B10" t="str">
-        <v>emo3</v>
+        <v>q9</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
@@ -919,30 +1225,48 @@
         <v>情绪状态</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>学生很难表达或调节当前感受。</v>
       </c>
-      <c r="F10" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I10" t="str">
         <v>否</v>
       </c>
-      <c r="H10" t="str">
-        <v>1</v>
-      </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
         <v>是</v>
       </c>
-      <c r="J10" t="str">
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>compute</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B11" t="str">
-        <v>soc1</v>
+        <v>q10</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
@@ -951,30 +1275,48 @@
         <v>同伴社交</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>与同伴的冲突、排斥或孤立反复发生。</v>
       </c>
-      <c r="F11" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I11" t="str">
         <v>否</v>
       </c>
-      <c r="H11" t="str">
-        <v>1</v>
-      </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
         <v>是</v>
       </c>
-      <c r="J11" t="str">
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>compute</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B12" t="str">
-        <v>soc2</v>
+        <v>q11</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
@@ -983,30 +1325,48 @@
         <v>同伴社交</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>学生缺少稳定的同伴支持。</v>
       </c>
-      <c r="F12" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I12" t="str">
         <v>否</v>
       </c>
-      <c r="H12" t="str">
-        <v>1</v>
-      </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
         <v>是</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>compute</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B13" t="str">
-        <v>soc3</v>
+        <v>q12</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
@@ -1015,30 +1375,48 @@
         <v>同伴社交</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>常规关系修复方式效果有限。</v>
       </c>
-      <c r="F13" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I13" t="str">
         <v>否</v>
       </c>
-      <c r="H13" t="str">
-        <v>1</v>
-      </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
         <v>是</v>
       </c>
-      <c r="J13" t="str">
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>compute</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B14" t="str">
-        <v>adp1</v>
+        <v>q13</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1047,30 +1425,48 @@
         <v>适应状况</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>在转班、家庭变化或重要事件后持续难以适应。</v>
       </c>
-      <c r="F14" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I14" t="str">
         <v>否</v>
       </c>
-      <c r="H14" t="str">
-        <v>1</v>
-      </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
         <v>是</v>
       </c>
-      <c r="J14" t="str">
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>compute</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B15" t="str">
-        <v>adp2</v>
+        <v>q14</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
@@ -1079,30 +1475,48 @@
         <v>适应状况</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>出现明显躯体不适、拒学或回避。</v>
       </c>
-      <c r="F15" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I15" t="str">
         <v>否</v>
       </c>
-      <c r="H15" t="str">
-        <v>1</v>
-      </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
         <v>是</v>
       </c>
-      <c r="J15" t="str">
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v>compute</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B16" t="str">
-        <v>adp3</v>
+        <v>q15</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
@@ -1111,30 +1525,48 @@
         <v>适应状况</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>问题持续四周以上且没有改善趋势。</v>
       </c>
-      <c r="F16" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I16" t="str">
         <v>否</v>
       </c>
-      <c r="H16" t="str">
-        <v>1</v>
-      </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
         <v>是</v>
       </c>
-      <c r="J16" t="str">
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>compute</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B17" t="str">
-        <v>ob1</v>
+        <v>q1</v>
       </c>
       <c r="C17" t="str">
         <v>single</v>
@@ -1143,30 +1575,48 @@
         <v>诱因清晰度</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>行为发生前的情境难以识别。</v>
       </c>
-      <c r="F17" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I17" t="str">
         <v>否</v>
       </c>
-      <c r="H17" t="str">
-        <v>1</v>
-      </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
         <v>是</v>
       </c>
-      <c r="J17" t="str">
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v>compute</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B18" t="str">
-        <v>ob2</v>
+        <v>q2</v>
       </c>
       <c r="C18" t="str">
         <v>single</v>
@@ -1175,30 +1625,48 @@
         <v>诱因清晰度</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
         <v>同样的情境下行为反应不一致。</v>
       </c>
-      <c r="F18" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I18" t="str">
         <v>否</v>
       </c>
-      <c r="H18" t="str">
-        <v>1</v>
-      </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
         <v>是</v>
       </c>
-      <c r="J18" t="str">
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <v>compute</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B19" t="str">
-        <v>ob3</v>
+        <v>q3</v>
       </c>
       <c r="C19" t="str">
         <v>single</v>
@@ -1207,30 +1675,48 @@
         <v>功能影响</v>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
         <v>该表现已影响学生完成日常学习任务。</v>
       </c>
-      <c r="F19" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I19" t="str">
         <v>否</v>
       </c>
-      <c r="H19" t="str">
-        <v>1</v>
-      </c>
-      <c r="I19" t="str">
+      <c r="J19" t="str">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
         <v>是</v>
       </c>
-      <c r="J19" t="str">
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
         <v>compute</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B20" t="str">
-        <v>ob4</v>
+        <v>q4</v>
       </c>
       <c r="C20" t="str">
         <v>single</v>
@@ -1239,30 +1725,48 @@
         <v>功能影响</v>
       </c>
       <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
         <v>该表现已影响学生与他人的正常互动。</v>
       </c>
-      <c r="F20" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I20" t="str">
         <v>否</v>
       </c>
-      <c r="H20" t="str">
-        <v>1</v>
-      </c>
-      <c r="I20" t="str">
+      <c r="J20" t="str">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
         <v>是</v>
       </c>
-      <c r="J20" t="str">
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
         <v>compute</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B21" t="str">
-        <v>ob5</v>
+        <v>q5</v>
       </c>
       <c r="C21" t="str">
         <v>single</v>
@@ -1271,30 +1775,48 @@
         <v>既有支持有效性</v>
       </c>
       <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
         <v>已尝试的座位调整、谈话等措施没有带来改善。</v>
       </c>
-      <c r="F21" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I21" t="str">
         <v>否</v>
       </c>
-      <c r="H21" t="str">
-        <v>1</v>
-      </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
         <v>是</v>
       </c>
-      <c r="J21" t="str">
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
         <v>compute</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B22" t="str">
-        <v>ob6</v>
+        <v>q6</v>
       </c>
       <c r="C22" t="str">
         <v>single</v>
@@ -1303,34 +1825,52 @@
         <v>既有支持有效性</v>
       </c>
       <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
         <v>家庭配合的支持措施没有带来改善。</v>
       </c>
-      <c r="F22" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I22" t="str">
         <v>否</v>
       </c>
-      <c r="H22" t="str">
-        <v>1</v>
-      </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
+        <v>1</v>
+      </c>
+      <c r="K22" t="str">
         <v>是</v>
       </c>
-      <c r="J22" t="str">
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
         <v>compute</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1348,13 +1888,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>几乎没有</v>
+        <v>完全不符合</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1362,13 +1902,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>很少</v>
+        <v>比较不符合</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1376,13 +1916,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>有时</v>
+        <v>一般</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1390,13 +1930,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>经常</v>
+        <v>比较符合</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1404,98 +1944,28 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>几乎每天</v>
+        <v>非常符合</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B7" t="str">
-        <v>1</v>
-      </c>
-      <c r="C7" t="str">
-        <v>完全不符合</v>
-      </c>
-      <c r="D7" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2</v>
-      </c>
-      <c r="C8" t="str">
-        <v>比较不符合</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B9" t="str">
-        <v>3</v>
-      </c>
-      <c r="C9" t="str">
-        <v>一般</v>
-      </c>
-      <c r="D9" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B10" t="str">
-        <v>4</v>
-      </c>
-      <c r="C10" t="str">
-        <v>比较符合</v>
-      </c>
-      <c r="D10" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B11" t="str">
-        <v>5</v>
-      </c>
-      <c r="C11" t="str">
-        <v>非常符合</v>
-      </c>
-      <c r="D11" t="str">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1525,19 +1995,25 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
+      <c r="J1" t="str">
+        <v>常模均值</v>
+      </c>
+      <c r="K1" t="str">
+        <v>常模标准差</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>SC_ACADEMIC</v>
+        <v>SC_S1D1</v>
       </c>
       <c r="C2" t="str">
         <v>学业表现</v>
       </c>
       <c r="D2" t="str">
-        <v>aca1,aca2,aca3</v>
+        <v>q1,q2,q3</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1554,19 +2030,25 @@
       <c r="I2" t="str">
         <v>学业表现稳定</v>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>SC_BEHAVIOR</v>
+        <v>SC_S1D2</v>
       </c>
       <c r="C3" t="str">
         <v>行为表现</v>
       </c>
       <c r="D3" t="str">
-        <v>beh1,beh2,beh3</v>
+        <v>q4,q5,q6</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1583,19 +2065,25 @@
       <c r="I3" t="str">
         <v>行为表现可控</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>SC_EMOTION</v>
+        <v>SC_S1D3</v>
       </c>
       <c r="C4" t="str">
         <v>情绪状态</v>
       </c>
       <c r="D4" t="str">
-        <v>emo1,emo2,emo3</v>
+        <v>q7,q8,q9</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1612,19 +2100,25 @@
       <c r="I4" t="str">
         <v>情绪状态平稳</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>SC_SOCIAL</v>
+        <v>SC_S1D4</v>
       </c>
       <c r="C5" t="str">
         <v>同伴社交</v>
       </c>
       <c r="D5" t="str">
-        <v>soc1,soc2,soc3</v>
+        <v>q10,q11,q12</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1641,19 +2135,25 @@
       <c r="I5" t="str">
         <v>同伴关系稳定</v>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>SC_ADAPT</v>
+        <v>SC_S1D5</v>
       </c>
       <c r="C6" t="str">
         <v>适应状况</v>
       </c>
       <c r="D6" t="str">
-        <v>adp1,adp2,adp3</v>
+        <v>q13,q14,q15</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1670,19 +2170,25 @@
       <c r="I6" t="str">
         <v>适应良好</v>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>SC_TRIGGER</v>
+        <v>SC_S2D1</v>
       </c>
       <c r="C7" t="str">
         <v>诱因清晰度</v>
       </c>
       <c r="D7" t="str">
-        <v>ob1,ob2</v>
+        <v>q1,q2</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1699,19 +2205,25 @@
       <c r="I7" t="str">
         <v>诱因清晰可干预</v>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B8" t="str">
-        <v>SC_FUNCTION</v>
+        <v>SC_S2D2</v>
       </c>
       <c r="C8" t="str">
         <v>功能影响</v>
       </c>
       <c r="D8" t="str">
-        <v>ob3,ob4</v>
+        <v>q3,q4</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -1728,19 +2240,25 @@
       <c r="I8" t="str">
         <v>功能影响有限</v>
       </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="B9" t="str">
-        <v>SC_SUPPORT_TRIED</v>
+        <v>SC_S2D3</v>
       </c>
       <c r="C9" t="str">
         <v>既有支持有效性</v>
       </c>
       <c r="D9" t="str">
-        <v>ob5,ob6</v>
+        <v>q5,q6</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>
@@ -1757,10 +2275,16 @@
       <c r="I9" t="str">
         <v>既有支持有效</v>
       </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/student_case/assessment.xlsx
+++ b/business-libraries/test-data/student_case/assessment.xlsx
@@ -523,10 +523,10 @@
         <v>SC_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>学生个体问题快速筛查</v>
+        <v>信号筛查</v>
       </c>
       <c r="C2" t="str">
-        <v>五类筛查</v>
+        <v>五维信号筛查</v>
       </c>
       <c r="D2" t="str">
         <v>student_case</v>
@@ -544,7 +544,7 @@
         <v>teacher</v>
       </c>
       <c r="I2" t="str">
-        <v>self_report</v>
+        <v>observation</v>
       </c>
       <c r="J2" t="str">
         <v>manual</v>
@@ -556,7 +556,7 @@
         <v>是</v>
       </c>
       <c r="M2" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -565,10 +565,10 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v/>
+        <v>学期初全班普查或速查模式（约 3 分钟）</v>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>180</v>
       </c>
       <c r="R2" t="str">
         <v/>
@@ -589,7 +589,7 @@
         <v>班主任</v>
       </c>
       <c r="X2" t="str">
-        <v>sensitive</v>
+        <v>highly_sensitive</v>
       </c>
       <c r="Y2" t="str">
         <v>proprietary</v>
@@ -598,13 +598,13 @@
         <v/>
       </c>
       <c r="AA2" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
       <c r="AB2" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AC2" t="str">
-        <v>从学业、行为、情绪、社交和适应五类表现进行教育场景筛查，不构成医学诊断。</v>
+        <v>15 题信号型题目（Track A）：教师按频率评定学生问题信号的出现频次（FREQ_5），按映射矩阵将权重（核心 5/关联 3）累加至十五型编码，积分≥5 激活。用于全班普查与学期初筛查，单独可输出初步编码和响应级别。</v>
       </c>
       <c r="AD2" t="str">
         <v/>
@@ -639,10 +639,10 @@
         <v>SC_S2</v>
       </c>
       <c r="B3" t="str">
-        <v>EBRCA 结构化观察记录</v>
+        <v>六维能力评估</v>
       </c>
       <c r="C3" t="str">
-        <v>EBRCA</v>
+        <v>六维评估</v>
       </c>
       <c r="D3" t="str">
         <v>student_case</v>
@@ -660,7 +660,7 @@
         <v>teacher</v>
       </c>
       <c r="I3" t="str">
-        <v>self_report</v>
+        <v>observation</v>
       </c>
       <c r="J3" t="str">
         <v>manual</v>
@@ -672,7 +672,7 @@
         <v>否</v>
       </c>
       <c r="M3" t="str">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N3" t="str">
         <v/>
@@ -681,10 +681,10 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>速查模式发现信号后补做，或 L2/L3 级学生深度评估</v>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>90</v>
       </c>
       <c r="R3" t="str">
         <v>SC_S1</v>
@@ -693,10 +693,10 @@
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>量表[SC_S1].均分 &gt;= 3.2 或 量表[SC_S1].维度[SC_S1D3] &gt;= 3.5</v>
+        <v>量表[SC_S1].总分 &gt;= 18</v>
       </c>
       <c r="U3" t="str">
-        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
+        <v>信号筛查出现信号（总分≥18）或需要深度评估时，建议补做后 30 题</v>
       </c>
       <c r="V3" t="str">
         <v>teacher_only</v>
@@ -705,7 +705,7 @@
         <v>班主任</v>
       </c>
       <c r="X3" t="str">
-        <v>sensitive</v>
+        <v>highly_sensitive</v>
       </c>
       <c r="Y3" t="str">
         <v>proprietary</v>
@@ -714,13 +714,13 @@
         <v/>
       </c>
       <c r="AA3" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
       <c r="AB3" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AC3" t="str">
-        <v>五类问题整体偏重、或情绪维度突出时，再做 EBRCA 深度归因</v>
+        <v>30 题能力型题目（Track B，Q16-Q45）：教师按频率评定学生「能做到」的频次（FREQ_5），每维度 5 题求和（满分 25），对照 A-E 等级（A≥22/B 18-21/C 13-17/D 8-12/E≤7），统计 D/E 维度数量与 Track A 编码交叉验证。</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -759,7 +759,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -822,19 +822,19 @@
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>学业表现</v>
+        <v>安全防护</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>学习表现近期出现持续且明显的下降。</v>
+        <v>是否有体罚、暴力或忽视迹象</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I2" t="str">
         <v>否</v>
@@ -872,19 +872,19 @@
         <v>single</v>
       </c>
       <c r="D3" t="str">
-        <v>学业表现</v>
+        <v>安全防护</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>完成作业、听课或考试受到明显影响。</v>
+        <v>是否被欺凌或明显排斥</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I3" t="str">
         <v>否</v>
@@ -922,19 +922,19 @@
         <v>single</v>
       </c>
       <c r="D4" t="str">
-        <v>学业表现</v>
+        <v>学会学习</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>已有常规支持措施没有带来改善。</v>
+        <v>是否有科目持续低于75分</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
@@ -972,19 +972,19 @@
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>行为表现</v>
+        <v>学会学习</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>冲动、对抗或规则破坏行为频繁出现。</v>
+        <v>作业是否经常不交或敷衍了事</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
@@ -1022,19 +1022,19 @@
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>行为表现</v>
+        <v>学会学习</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>行为已经明显影响本人或同伴的学习。</v>
+        <v>是否需反复催促才开始学习任务</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
@@ -1072,19 +1072,19 @@
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>行为表现</v>
+        <v>行为适应</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>行为发生的场景和诱因较难预测。</v>
+        <v>是否每天被点名提醒2次及以上</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I7" t="str">
         <v>否</v>
@@ -1122,19 +1122,19 @@
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>情绪状态</v>
+        <v>行为适应</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>持续出现低落、焦虑、易怒或明显退缩。</v>
+        <v>一周内是否发生肢体冲突</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I8" t="str">
         <v>否</v>
@@ -1172,19 +1172,19 @@
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>情绪状态</v>
+        <v>行为适应</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>情绪变化已经影响日常功能。</v>
+        <v>物品整理是否长期混乱、常丢东西</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I9" t="str">
         <v>否</v>
@@ -1222,19 +1222,19 @@
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>情绪状态</v>
+        <v>情绪管理</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>学生很难表达或调节当前感受。</v>
+        <v>是否从不或极少主动举手发言</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I10" t="str">
         <v>否</v>
@@ -1272,19 +1272,19 @@
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>同伴社交</v>
+        <v>情绪管理</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>与同伴的冲突、排斥或孤立反复发生。</v>
+        <v>是否有与情境不成比例的强烈情绪</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I11" t="str">
         <v>否</v>
@@ -1322,19 +1322,19 @@
         <v>single</v>
       </c>
       <c r="D12" t="str">
-        <v>同伴社交</v>
+        <v>情绪管理</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>学生缺少稳定的同伴支持。</v>
+        <v>是否常说「我不行」「我太笨了」</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I12" t="str">
         <v>否</v>
@@ -1372,19 +1372,19 @@
         <v>single</v>
       </c>
       <c r="D13" t="str">
-        <v>同伴社交</v>
+        <v>人际关系</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>常规关系修复方式效果有限。</v>
+        <v>自由活动时间是否通常独自一人</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I13" t="str">
         <v>否</v>
@@ -1422,19 +1422,19 @@
         <v>single</v>
       </c>
       <c r="D14" t="str">
-        <v>适应状况</v>
+        <v>人际关系</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>在转班、家庭变化或重要事件后持续难以适应。</v>
+        <v>是否不会用恰当方式加入同伴游戏</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I14" t="str">
         <v>否</v>
@@ -1472,19 +1472,19 @@
         <v>single</v>
       </c>
       <c r="D15" t="str">
-        <v>适应状况</v>
+        <v>家庭环境</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>出现明显躯体不适、拒学或回避。</v>
+        <v>亲子沟通是否存在明显障碍</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I15" t="str">
         <v>否</v>
@@ -1522,19 +1522,19 @@
         <v>single</v>
       </c>
       <c r="D16" t="str">
-        <v>适应状况</v>
+        <v>家庭环境</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>问题持续四周以上且没有改善趋势。</v>
+        <v>家庭支持是否明显缺位</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I16" t="str">
         <v>否</v>
@@ -1572,22 +1572,22 @@
         <v>single</v>
       </c>
       <c r="D17" t="str">
-        <v>诱因清晰度</v>
+        <v>自我意识</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>行为发生前的情境难以识别。</v>
+        <v>能否准确说出自己的姓名、年龄、性别和所在班级</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I17" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J17" t="str">
         <v>1</v>
@@ -1622,22 +1622,22 @@
         <v>single</v>
       </c>
       <c r="D18" t="str">
-        <v>诱因清晰度</v>
+        <v>自我意识</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>同样的情境下行为反应不一致。</v>
+        <v>能否识别并说出自己当前的情绪状态（开心/生气/难过/害怕）</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I18" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J18" t="str">
         <v>1</v>
@@ -1672,22 +1672,22 @@
         <v>single</v>
       </c>
       <c r="D19" t="str">
-        <v>功能影响</v>
+        <v>自我意识</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>该表现已影响学生完成日常学习任务。</v>
+        <v>能否说出自己的至少2个优点或擅长的事情</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I19" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J19" t="str">
         <v>1</v>
@@ -1722,22 +1722,22 @@
         <v>single</v>
       </c>
       <c r="D20" t="str">
-        <v>功能影响</v>
+        <v>自我意识</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>该表现已影响学生与他人的正常互动。</v>
+        <v>在做错事时能否承认自己的错误，不推卸责任</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I20" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J20" t="str">
         <v>1</v>
@@ -1772,22 +1772,22 @@
         <v>single</v>
       </c>
       <c r="D21" t="str">
-        <v>既有支持有效性</v>
+        <v>自我意识</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>已尝试的座位调整、谈话等措施没有带来改善。</v>
+        <v>对自己的能力是否有基本信心，愿意尝试新任务</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I21" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J21" t="str">
         <v>1</v>
@@ -1822,22 +1822,22 @@
         <v>single</v>
       </c>
       <c r="D22" t="str">
-        <v>既有支持有效性</v>
+        <v>社会适应</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>家庭配合的支持措施没有带来改善。</v>
+        <v>能否遵守课堂基本规则（举手发言、不随意离开座位）</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I22" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J22" t="str">
         <v>1</v>
@@ -1858,12 +1858,1212 @@
         <v/>
       </c>
       <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>q7</v>
+      </c>
+      <c r="C23" t="str">
+        <v>single</v>
+      </c>
+      <c r="D23" t="str">
+        <v>社会适应</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>能否按时完成学校基本作息（准时到校、交作业、值日）</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I23" t="str">
+        <v>是</v>
+      </c>
+      <c r="J23" t="str">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>是</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B24" t="str">
+        <v>q8</v>
+      </c>
+      <c r="C24" t="str">
+        <v>single</v>
+      </c>
+      <c r="D24" t="str">
+        <v>社会适应</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>在小组合作中能否完成分配的任务，配合他人工作</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I24" t="str">
+        <v>是</v>
+      </c>
+      <c r="J24" t="str">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>是</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B25" t="str">
+        <v>q9</v>
+      </c>
+      <c r="C25" t="str">
+        <v>single</v>
+      </c>
+      <c r="D25" t="str">
+        <v>社会适应</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>面对规则变化或临时调课时，能否适应而不表现过度焦虑</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I25" t="str">
+        <v>是</v>
+      </c>
+      <c r="J25" t="str">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>是</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B26" t="str">
+        <v>q10</v>
+      </c>
+      <c r="C26" t="str">
+        <v>single</v>
+      </c>
+      <c r="D26" t="str">
+        <v>社会适应</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>在不同教师的课堂上，行为是否基本一致</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I26" t="str">
+        <v>是</v>
+      </c>
+      <c r="J26" t="str">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>是</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B27" t="str">
+        <v>q11</v>
+      </c>
+      <c r="C27" t="str">
+        <v>single</v>
+      </c>
+      <c r="D27" t="str">
+        <v>情绪管理</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>情绪激动时，能否在教师或同伴安抚下逐渐平复</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I27" t="str">
+        <v>是</v>
+      </c>
+      <c r="J27" t="str">
+        <v>1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>是</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B28" t="str">
+        <v>q12</v>
+      </c>
+      <c r="C28" t="str">
+        <v>single</v>
+      </c>
+      <c r="D28" t="str">
+        <v>情绪管理</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>能否用语言（而非哭闹/攻击/摔东西）表达情绪需求</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I28" t="str">
+        <v>是</v>
+      </c>
+      <c r="J28" t="str">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>是</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B29" t="str">
+        <v>q13</v>
+      </c>
+      <c r="C29" t="str">
+        <v>single</v>
+      </c>
+      <c r="D29" t="str">
+        <v>情绪管理</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>面对「等一等」或「不可以」时，能否接受而不立即崩溃</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I29" t="str">
+        <v>是</v>
+      </c>
+      <c r="J29" t="str">
+        <v>1</v>
+      </c>
+      <c r="K29" t="str">
+        <v>是</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B30" t="str">
+        <v>q14</v>
+      </c>
+      <c r="C30" t="str">
+        <v>single</v>
+      </c>
+      <c r="D30" t="str">
+        <v>情绪管理</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>日常情绪状态是否基本稳定，无明显的大起大落</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I30" t="str">
+        <v>是</v>
+      </c>
+      <c r="J30" t="str">
+        <v>1</v>
+      </c>
+      <c r="K30" t="str">
+        <v>是</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B31" t="str">
+        <v>q15</v>
+      </c>
+      <c r="C31" t="str">
+        <v>single</v>
+      </c>
+      <c r="D31" t="str">
+        <v>情绪管理</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>面对挫折时，能否自我安抚或主动求助</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I31" t="str">
+        <v>是</v>
+      </c>
+      <c r="J31" t="str">
+        <v>1</v>
+      </c>
+      <c r="K31" t="str">
+        <v>是</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B32" t="str">
+        <v>q16</v>
+      </c>
+      <c r="C32" t="str">
+        <v>single</v>
+      </c>
+      <c r="D32" t="str">
+        <v>人际关系</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>课间自由活动时，是否有固定的玩伴或朋友</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I32" t="str">
+        <v>是</v>
+      </c>
+      <c r="J32" t="str">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>是</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B33" t="str">
+        <v>q17</v>
+      </c>
+      <c r="C33" t="str">
+        <v>single</v>
+      </c>
+      <c r="D33" t="str">
+        <v>人际关系</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>能否与同学分享文具、玩具或活动空间</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I33" t="str">
+        <v>是</v>
+      </c>
+      <c r="J33" t="str">
+        <v>1</v>
+      </c>
+      <c r="K33" t="str">
+        <v>是</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B34" t="str">
+        <v>q18</v>
+      </c>
+      <c r="C34" t="str">
+        <v>single</v>
+      </c>
+      <c r="D34" t="str">
+        <v>人际关系</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>与同学发生冲突时，能否尝试用语言解决而非动手</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I34" t="str">
+        <v>是</v>
+      </c>
+      <c r="J34" t="str">
+        <v>1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>是</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B35" t="str">
+        <v>q19</v>
+      </c>
+      <c r="C35" t="str">
+        <v>single</v>
+      </c>
+      <c r="D35" t="str">
+        <v>人际关系</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>能否主动加入或被邀请加入集体活动</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I35" t="str">
+        <v>是</v>
+      </c>
+      <c r="J35" t="str">
+        <v>1</v>
+      </c>
+      <c r="K35" t="str">
+        <v>是</v>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B36" t="str">
+        <v>q20</v>
+      </c>
+      <c r="C36" t="str">
+        <v>single</v>
+      </c>
+      <c r="D36" t="str">
+        <v>人际关系</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>能否理解他人的情绪并做出适当回应</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I36" t="str">
+        <v>是</v>
+      </c>
+      <c r="J36" t="str">
+        <v>1</v>
+      </c>
+      <c r="K36" t="str">
+        <v>是</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B37" t="str">
+        <v>q21</v>
+      </c>
+      <c r="C37" t="str">
+        <v>single</v>
+      </c>
+      <c r="D37" t="str">
+        <v>学会学习</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>课堂上能否保持与年级相当的有效注意时间</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I37" t="str">
+        <v>是</v>
+      </c>
+      <c r="J37" t="str">
+        <v>1</v>
+      </c>
+      <c r="K37" t="str">
+        <v>是</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B38" t="str">
+        <v>q22</v>
+      </c>
+      <c r="C38" t="str">
+        <v>single</v>
+      </c>
+      <c r="D38" t="str">
+        <v>学会学习</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>能否按步骤独立完成课堂任务</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I38" t="str">
+        <v>是</v>
+      </c>
+      <c r="J38" t="str">
+        <v>1</v>
+      </c>
+      <c r="K38" t="str">
+        <v>是</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B39" t="str">
+        <v>q23</v>
+      </c>
+      <c r="C39" t="str">
+        <v>single</v>
+      </c>
+      <c r="D39" t="str">
+        <v>学会学习</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>遇到学习困难时，能否主动提问或寻求帮助</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I39" t="str">
+        <v>是</v>
+      </c>
+      <c r="J39" t="str">
+        <v>1</v>
+      </c>
+      <c r="K39" t="str">
+        <v>是</v>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B40" t="str">
+        <v>q24</v>
+      </c>
+      <c r="C40" t="str">
+        <v>single</v>
+      </c>
+      <c r="D40" t="str">
+        <v>学会学习</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>能否使用至少一种基础学习策略（划线/复述/提纲/笔记）</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I40" t="str">
+        <v>是</v>
+      </c>
+      <c r="J40" t="str">
+        <v>1</v>
+      </c>
+      <c r="K40" t="str">
+        <v>是</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B41" t="str">
+        <v>q25</v>
+      </c>
+      <c r="C41" t="str">
+        <v>single</v>
+      </c>
+      <c r="D41" t="str">
+        <v>学会学习</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>对自己的学习效果是否有基本判断（知道哪里会、哪里不会）</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I41" t="str">
+        <v>是</v>
+      </c>
+      <c r="J41" t="str">
+        <v>1</v>
+      </c>
+      <c r="K41" t="str">
+        <v>是</v>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B42" t="str">
+        <v>q26</v>
+      </c>
+      <c r="C42" t="str">
+        <v>single</v>
+      </c>
+      <c r="D42" t="str">
+        <v>生涯认知</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>能否说出至少2种常见职业及其基本工作内容</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I42" t="str">
+        <v>是</v>
+      </c>
+      <c r="J42" t="str">
+        <v>1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>是</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B43" t="str">
+        <v>q27</v>
+      </c>
+      <c r="C43" t="str">
+        <v>single</v>
+      </c>
+      <c r="D43" t="str">
+        <v>生涯认知</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>是否在角色扮演/游戏/课堂活动中表现出职业兴趣</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I43" t="str">
+        <v>是</v>
+      </c>
+      <c r="J43" t="str">
+        <v>1</v>
+      </c>
+      <c r="K43" t="str">
+        <v>是</v>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B44" t="str">
+        <v>q28</v>
+      </c>
+      <c r="C44" t="str">
+        <v>single</v>
+      </c>
+      <c r="D44" t="str">
+        <v>生涯认知</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>能否清楚说出自己感兴趣的学科或活动</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I44" t="str">
+        <v>是</v>
+      </c>
+      <c r="J44" t="str">
+        <v>1</v>
+      </c>
+      <c r="K44" t="str">
+        <v>是</v>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B45" t="str">
+        <v>q29</v>
+      </c>
+      <c r="C45" t="str">
+        <v>single</v>
+      </c>
+      <c r="D45" t="str">
+        <v>生涯认知</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>能否将当前学习内容与未来想做之事建立简单联系</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I45" t="str">
+        <v>是</v>
+      </c>
+      <c r="J45" t="str">
+        <v>1</v>
+      </c>
+      <c r="K45" t="str">
+        <v>是</v>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B46" t="str">
+        <v>q30</v>
+      </c>
+      <c r="C46" t="str">
+        <v>single</v>
+      </c>
+      <c r="D46" t="str">
+        <v>生涯认知</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>对自己的课余兴趣是否有基本认知，能坚持参与至少一项</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I46" t="str">
+        <v>是</v>
+      </c>
+      <c r="J46" t="str">
+        <v>1</v>
+      </c>
+      <c r="K46" t="str">
+        <v>是</v>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P46"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1888,13 +3088,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>完全不符合</v>
+        <v>几乎没有</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1902,13 +3102,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>比较不符合</v>
+        <v>很少</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1916,13 +3116,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>一般</v>
+        <v>有时</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1930,13 +3130,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>比较符合</v>
+        <v>经常</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1944,13 +3144,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>非常符合</v>
+        <v>几乎每天</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
@@ -1965,7 +3165,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2010,25 +3210,25 @@
         <v>SC_S1D1</v>
       </c>
       <c r="C2" t="str">
-        <v>学业表现</v>
+        <v>安全防护</v>
       </c>
       <c r="D2" t="str">
-        <v>q1,q2,q3</v>
+        <v>q1,q2</v>
       </c>
       <c r="E2" t="str">
-        <v>mean</v>
+        <v>sum</v>
       </c>
       <c r="F2" t="str">
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>学业表现维度</v>
+        <v>体罚/暴力/忽视与被欺凌/排斥等安全信号（纯信号维度，最高优先级）</v>
       </c>
       <c r="H2" t="str">
-        <v>学业表现持续下降且常规支持无效</v>
+        <v>维度总分≥6 标记为安全预警；任一题≥4 分直接触发红色紧急响应</v>
       </c>
       <c r="I2" t="str">
-        <v>学业表现稳定</v>
+        <v>维度总分&lt;6，无安全信号</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -2045,25 +3245,25 @@
         <v>SC_S1D2</v>
       </c>
       <c r="C3" t="str">
-        <v>行为表现</v>
+        <v>学会学习</v>
       </c>
       <c r="D3" t="str">
-        <v>q4,q5,q6</v>
+        <v>q3,q4,q5</v>
       </c>
       <c r="E3" t="str">
-        <v>mean</v>
+        <v>sum</v>
       </c>
       <c r="F3" t="str">
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>行为表现维度</v>
+        <v>成绩偏低、作业敷衍、需反复催促等学习信号</v>
       </c>
       <c r="H3" t="str">
-        <v>冲动或对抗行为频繁且难以预测</v>
+        <v>维度总分≥9（≥2 题触发）标记该维度</v>
       </c>
       <c r="I3" t="str">
-        <v>行为表现可控</v>
+        <v>维度总分&lt;9，暂不标记</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -2080,25 +3280,25 @@
         <v>SC_S1D3</v>
       </c>
       <c r="C4" t="str">
-        <v>情绪状态</v>
+        <v>行为适应</v>
       </c>
       <c r="D4" t="str">
-        <v>q7,q8,q9</v>
+        <v>q6,q7,q8</v>
       </c>
       <c r="E4" t="str">
-        <v>mean</v>
+        <v>sum</v>
       </c>
       <c r="F4" t="str">
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>情绪状态维度</v>
+        <v>课堂点名、肢体冲突、物品混乱等行为信号</v>
       </c>
       <c r="H4" t="str">
-        <v>持续低落焦虑且影响日常功能</v>
+        <v>维度总分≥9（≥2 题触发）标记该维度</v>
       </c>
       <c r="I4" t="str">
-        <v>情绪状态平稳</v>
+        <v>维度总分&lt;9，暂不标记</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -2115,25 +3315,25 @@
         <v>SC_S1D4</v>
       </c>
       <c r="C5" t="str">
-        <v>同伴社交</v>
+        <v>情绪管理</v>
       </c>
       <c r="D5" t="str">
-        <v>q10,q11,q12</v>
+        <v>q9,q10,q11</v>
       </c>
       <c r="E5" t="str">
-        <v>mean</v>
+        <v>sum</v>
       </c>
       <c r="F5" t="str">
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>同伴社交维度</v>
+        <v>不举手、情绪过激、自我否定等情绪信号</v>
       </c>
       <c r="H5" t="str">
-        <v>冲突或孤立反复发生且修复无效</v>
+        <v>维度总分≥9（≥2 题触发）标记该维度</v>
       </c>
       <c r="I5" t="str">
-        <v>同伴关系稳定</v>
+        <v>维度总分&lt;9，暂不标记</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -2150,25 +3350,25 @@
         <v>SC_S1D5</v>
       </c>
       <c r="C6" t="str">
-        <v>适应状况</v>
+        <v>人际关系</v>
       </c>
       <c r="D6" t="str">
-        <v>q13,q14,q15</v>
+        <v>q12,q13</v>
       </c>
       <c r="E6" t="str">
-        <v>mean</v>
+        <v>sum</v>
       </c>
       <c r="F6" t="str">
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>适应状况维度</v>
+        <v>独处、不会加入同伴游戏等社交信号</v>
       </c>
       <c r="H6" t="str">
-        <v>出现拒学、躯体化且持续四周以上</v>
+        <v>维度总分≥6（≥2 题触发）标记该维度</v>
       </c>
       <c r="I6" t="str">
-        <v>适应良好</v>
+        <v>维度总分&lt;6，暂不标记</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -2179,31 +3379,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SC_S2</v>
+        <v>SC_S1</v>
       </c>
       <c r="B7" t="str">
-        <v>SC_S2D1</v>
+        <v>SC_S1D6</v>
       </c>
       <c r="C7" t="str">
-        <v>诱因清晰度</v>
+        <v>家庭环境</v>
       </c>
       <c r="D7" t="str">
-        <v>q1,q2</v>
+        <v>q14,q15</v>
       </c>
       <c r="E7" t="str">
-        <v>mean</v>
+        <v>sum</v>
       </c>
       <c r="F7" t="str">
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>诱因清晰度维度</v>
+        <v>亲子沟通障碍、家庭支持缺位等家庭信号（纯信号维度，无 6D 能力对应）</v>
       </c>
       <c r="H7" t="str">
-        <v>诱因不明确，行为难以预防</v>
+        <v>维度总分≥6 标记该维度；E 类编码激活直接触发高响应</v>
       </c>
       <c r="I7" t="str">
-        <v>诱因清晰可干预</v>
+        <v>维度总分&lt;6，暂不标记</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -2217,28 +3417,28 @@
         <v>SC_S2</v>
       </c>
       <c r="B8" t="str">
-        <v>SC_S2D2</v>
+        <v>SC_S2D1</v>
       </c>
       <c r="C8" t="str">
-        <v>功能影响</v>
+        <v>自我意识</v>
       </c>
       <c r="D8" t="str">
-        <v>q3,q4</v>
+        <v>q1,q2,q3,q4,q5</v>
       </c>
       <c r="E8" t="str">
-        <v>mean</v>
+        <v>sum</v>
       </c>
       <c r="F8" t="str">
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v>功能影响维度</v>
+        <v>认识自己基本属性、情绪状态、个人优势和局限的能力（基本身份认知、情绪识别、自我评价和错误承认）</v>
       </c>
       <c r="H8" t="str">
-        <v>已明显影响学习与生活功能</v>
+        <v>维度分≥18（原始分≤12，D/E 级）：自我认知严重不足或模糊，需重点关注</v>
       </c>
       <c r="I8" t="str">
-        <v>功能影响有限</v>
+        <v>维度分≤12（原始分≥18，A/B 级）：自我认知发展良好</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -2252,39 +3452,179 @@
         <v>SC_S2</v>
       </c>
       <c r="B9" t="str">
+        <v>SC_S2D2</v>
+      </c>
+      <c r="C9" t="str">
+        <v>社会适应</v>
+      </c>
+      <c r="D9" t="str">
+        <v>q6,q7,q8,q9,q10</v>
+      </c>
+      <c r="E9" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F9" t="str">
+        <v>1</v>
+      </c>
+      <c r="G9" t="str">
+        <v>遵守规则、完成学校基本作息、参与集体活动的能力（课堂适应、学校规则、集体责任感）</v>
+      </c>
+      <c r="H9" t="str">
+        <v>维度分≥18（原始分≤12，D/E 级）：经常违反规则或需要大量外部约束，需重点关注</v>
+      </c>
+      <c r="I9" t="str">
+        <v>维度分≤12（原始分≥18，A/B 级）：规则遵守与集体适应良好</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B10" t="str">
         <v>SC_S2D3</v>
       </c>
-      <c r="C9" t="str">
-        <v>既有支持有效性</v>
-      </c>
-      <c r="D9" t="str">
-        <v>q5,q6</v>
-      </c>
-      <c r="E9" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F9" t="str">
-        <v>1</v>
-      </c>
-      <c r="G9" t="str">
-        <v>既有支持有效性维度</v>
-      </c>
-      <c r="H9" t="str">
-        <v>已尝试的支持基本无效</v>
-      </c>
-      <c r="I9" t="str">
-        <v>既有支持有效</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
+      <c r="C10" t="str">
+        <v>情绪管理</v>
+      </c>
+      <c r="D10" t="str">
+        <v>q11,q12,q13,q14,q15</v>
+      </c>
+      <c r="E10" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F10" t="str">
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
+        <v>识别、表达和调控自身情绪的能力（情绪识别准确性、表达适度性、调节策略有效性）</v>
+      </c>
+      <c r="H10" t="str">
+        <v>维度分≥18（原始分≤12，D/E 级）：情绪经常失控或调节策略缺失，需重点关注</v>
+      </c>
+      <c r="I10" t="str">
+        <v>维度分≤12（原始分≥18，A/B 级）：情绪识别与调节能力良好</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B11" t="str">
+        <v>SC_S2D4</v>
+      </c>
+      <c r="C11" t="str">
+        <v>人际关系</v>
+      </c>
+      <c r="D11" t="str">
+        <v>q16,q17,q18,q19,q20</v>
+      </c>
+      <c r="E11" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <v>建立和维持同伴关系、理解和回应他人社交信号的能力（交友动机、社交技能、冲突处理）</v>
+      </c>
+      <c r="H11" t="str">
+        <v>维度分≥18（原始分≤12，D/E 级）：经常独自一人或频繁冲突，需重点关注</v>
+      </c>
+      <c r="I11" t="str">
+        <v>维度分≤12（原始分≥18，A/B 级）：同伴关系建立与维护良好</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B12" t="str">
+        <v>SC_S2D5</v>
+      </c>
+      <c r="C12" t="str">
+        <v>学会学习</v>
+      </c>
+      <c r="D12" t="str">
+        <v>q21,q22,q23,q24,q25</v>
+      </c>
+      <c r="E12" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F12" t="str">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v>掌握学习方法、自我规划和主动求知的能力（学习习惯、方法运用、时间管理）</v>
+      </c>
+      <c r="H12" t="str">
+        <v>维度分≥18（原始分≤12，D/E 级）：几乎没有学习方法或放弃学习尝试，需重点关注</v>
+      </c>
+      <c r="I12" t="str">
+        <v>维度分≤12（原始分≥18，A/B 级）：学习方法与自我规划良好</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="B13" t="str">
+        <v>SC_S2D6</v>
+      </c>
+      <c r="C13" t="str">
+        <v>生涯认知</v>
+      </c>
+      <c r="D13" t="str">
+        <v>q26,q27,q28,q29,q30</v>
+      </c>
+      <c r="E13" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F13" t="str">
+        <v>1</v>
+      </c>
+      <c r="G13" t="str">
+        <v>对未来、自我发展方向的初步思考和探索意愿（小学阶段以兴趣探索和成长意识为主）</v>
+      </c>
+      <c r="H13" t="str">
+        <v>维度分≥18（原始分≤12，D/E 级）：兴趣模糊或对未来无所谓，需关注</v>
+      </c>
+      <c r="I13" t="str">
+        <v>维度分≤12（原始分≥18，A/B 级）：兴趣探索与成长意识良好</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
   </ignoredErrors>
 </worksheet>
 </file>